--- a/PPREstimation/output/top10/13_2_Northern_Humboldt_Current_(1995-1998).xlsx
+++ b/PPREstimation/output/top10/13_2_Northern_Humboldt_Current_(1995-1998).xlsx
@@ -701,7 +701,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Non-consuming egg/detritus or external input pool; no catch assignment.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +789,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Non-consuming egg/detritus or external input pool; no catch assignment.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -869,7 +877,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Non-consuming egg/detritus or external input pool; no catch assignment.</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
       </c>
@@ -953,7 +965,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Non-consuming egg/detritus or external input pool; no catch assignment.</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
@@ -1037,7 +1053,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dermochelys coriacea; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n">
         <v>4.036651412301057</v>
       </c>
@@ -1121,7 +1141,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Chelonia mydas; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="n">
         <v>3.483659556323609</v>
       </c>
@@ -1205,7 +1229,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cetaceans; no species list documented.</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n">
         <v>4.211135921072626</v>
       </c>
@@ -1289,7 +1317,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Otaria flavescens; Arctocephalus australis; definition: not documented - no species list found for this source group.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
         <v>3.748751632707471</v>
       </c>
@@ -1373,7 +1405,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Phalacrocorax bougainvillii; Sula variegata; Pelecanus thagus; definition: not documented - no species list found for this source group.</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="n">
         <v>3.92938764796025</v>
       </c>
@@ -1457,7 +1493,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Chondrichthyans other than the separately modelled benthic elasmobranch pool; Table E aggregates as apex predatory fish.</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="n">
         <v>4.559153783576394</v>
       </c>
@@ -1541,7 +1581,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Galeichtys peruvianus; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>3.148778445321641</v>
       </c>
@@ -1625,7 +1669,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Prionotus stephanophrys; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>3.329151265268742</v>
       </c>
@@ -1709,7 +1757,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Medium sciaenids; no full species list documented. Ctenosciaena peruviana is explicitly in Small demersal fish. Table E aggregates as demersal benthivorous fish.</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>3.376461817236302</v>
       </c>
@@ -1793,7 +1845,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Paralabrax humeralis; Hemanthias peruanus; Mugil cephalus; definition: Medium demersal fishes, source examples Paralabrax, Hemanthias and Mugil; Table E aggregates as demersal benthivorous fish.</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
         <v>3.2413623234645</v>
       </c>
@@ -1877,7 +1933,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Congers; no species list documented. Table E aggregates as demersal piscivorous fish.</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="n">
         <v>4.165306519244008</v>
       </c>
@@ -1961,7 +2021,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Trachinotus paitensis; Stromateus stellatus; Peprilus medius; definition: Butter fishes; named examples Trachinotus, Stromateus and Peprilus. Table E aggregates as pelagic planktivorous fish.</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n">
         <v>2.633052892562976</v>
       </c>
@@ -2045,7 +2109,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Benthic elasmobranchs, separate from Chondrichthyans; Table E aggregates as demersal benthivorous fish.</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="n">
         <v>3.404504687960284</v>
       </c>
@@ -2129,7 +2197,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Odonthestes regia; Labrisomus philippi; Ctenosciaena peruviana; definition: Small demersal fishes; source examples take precedence over habitat heuristics. Table E aggregates as demersal planktivorous fish.</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
         <v>2.472727272727273</v>
       </c>
@@ -2213,7 +2285,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Paralichthys adspersus; Hippoglosina sp.; definition: Flatfishes; Table E aggregates as demersal piscivorous fish.</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="n">
         <v>3.92129953038265</v>
       </c>
@@ -2297,7 +2373,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>M. gayi peruanus; definition: Peruvian hake Merluccius gayi peruanus, &gt;50 cm. Printed interval endpoints retained; catch is unaged.</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
         <v>4.376603472176864</v>
       </c>
@@ -2381,7 +2461,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>M. gayi peruanus; definition: Peruvian hake Merluccius gayi peruanus, 30-49 cm. Printed interval endpoints retained; catch is unaged.</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="n">
         <v>3.867970436464992</v>
       </c>
@@ -2465,7 +2549,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Merluccius gayi peruanus; definition: Peruvian hake Merluccius gayi peruanus, &lt;29 cm. Printed interval endpoints retained; catch is unaged.</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="n">
         <v>3.730402926500451</v>
       </c>
@@ -2549,7 +2637,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sarda chiliensis; Coryphaena hippurus; Thunnus albacares; definition: Other large pelagic fishes; source examples are bonito, dolphinfish and yellowfin tuna. Table E calls the aggregate pelagic piscivorous fish.</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="n">
         <v>3.897127954782604</v>
       </c>
@@ -2633,7 +2725,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Scomber japonicus; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n">
         <v>3.601955384262967</v>
       </c>
@@ -2717,7 +2813,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Trachurus murphyi; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>3.445340771821614</v>
       </c>
@@ -2801,7 +2901,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Anchoa nasus; definition: Other small pelagic fish, excluding anchovy and sardine; Table E aggregates them as pelagic planktivorous fish.</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n">
         <v>2.768181818181818</v>
       </c>
@@ -2885,7 +2989,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Loligo gahi; Octopus vulgaris; Logigunculla sp.; definition: Cephalopods other than the separately modelled jumbo squid Dosidicus gigas.</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="n">
         <v>3.174424242424243</v>
       </c>
@@ -2969,7 +3077,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Dosidicus gigas; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="n">
         <v>4.086797321850294</v>
       </c>
@@ -3053,7 +3165,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Vinciguerria lucetia; Lampanyctus spp.; Leuroglossus spp.; definition: Mesopelagic fishes; species/genus examples in Tam (2008) section 2.1.</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="n">
         <v>3.284848484848485</v>
       </c>
@@ -3137,7 +3253,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Engraulis ringens; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="n">
         <v>2.934081345765596</v>
       </c>
@@ -3221,7 +3341,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sardinops sagax; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="n">
         <v>3.081475158660141</v>
       </c>
@@ -3305,7 +3429,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Benthic macroinvertebrates; no species membership list documented in focal paper, supplement or Tam predecessor.</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="n">
         <v>2.052631578947368</v>
       </c>
@@ -3389,7 +3517,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Chrysaora plocamia; definition: Named taxon; source spellings and verified aliases retained in members.csv.</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="n">
         <v>3.051393802259995</v>
       </c>
@@ -3473,7 +3605,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Small gelatinous zooplankton; Chrysaora plocamia is excluded into its own focal-model group.</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="n">
         <v>2.992424242424243</v>
       </c>
@@ -3557,7 +3693,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Macrozooplankton 2-20 mm.</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="n">
         <v>2.303030303030303</v>
       </c>
@@ -3641,7 +3781,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mesozooplankton 200-2000 micrometres.</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="n">
         <v>2.181818181818182</v>
       </c>
@@ -3725,7 +3869,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Microzooplankton 20-200 micrometres.</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="n">
         <v>2.212121212121212</v>
       </c>
@@ -3809,7 +3957,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Dinoflagellates and silicoflagellates.</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
@@ -3893,7 +4045,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Diatoms.</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
@@ -4159,7 +4315,9 @@
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
       </c>
@@ -4217,7 +4375,9 @@
       <c r="T3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V3" s="2" t="n">
         <v>0</v>
       </c>
@@ -4275,7 +4435,9 @@
       <c r="T4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
       </c>
@@ -4333,7 +4495,9 @@
       <c r="T5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
       </c>
@@ -4391,7 +4555,9 @@
       <c r="T6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
@@ -4447,7 +4613,9 @@
       <c r="T7" s="2" t="n">
         <v>93.3598933783363</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>329.8300526420346</v>
+      </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
       </c>
@@ -4503,7 +4671,9 @@
       <c r="T8" s="2" t="n">
         <v>38.9436369955784</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>130.9805801156029</v>
+      </c>
       <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
@@ -4559,7 +4729,9 @@
       <c r="T9" s="2" t="n">
         <v>4662.88804608467</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>15062.69347503343</v>
+      </c>
       <c r="V9" s="2" t="n">
         <v>0</v>
       </c>
@@ -4615,7 +4787,9 @@
       <c r="T10" s="2" t="n">
         <v>2978.011516236098</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>7852.979598968306</v>
+      </c>
       <c r="V10" s="2" t="n">
         <v>0</v>
       </c>
@@ -4671,7 +4845,9 @@
       <c r="T11" s="2" t="n">
         <v>14683.24346635239</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>40258.57746310868</v>
+      </c>
       <c r="V11" s="2" t="n">
         <v>0</v>
       </c>
@@ -4729,9 +4905,11 @@
       <c r="T12" s="2" t="n">
         <v>195.2023859866585</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>628.5731936635907</v>
+      </c>
       <c r="V12" s="2" t="n">
-        <v>8719.621807822547</v>
+        <v>9364.462679720415</v>
       </c>
     </row>
     <row r="13">
@@ -4787,9 +4965,11 @@
       <c r="T13" s="2" t="n">
         <v>8.15664640193301</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>20.74595787825953</v>
+      </c>
       <c r="V13" s="2" t="n">
-        <v>58.7795138381428</v>
+        <v>57.97407860326917</v>
       </c>
     </row>
     <row r="14">
@@ -4845,9 +5025,11 @@
       <c r="T14" s="2" t="n">
         <v>14.80448689328681</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>26.42535486733363</v>
+      </c>
       <c r="V14" s="2" t="n">
-        <v>120.6555955779325</v>
+        <v>122.7283630538291</v>
       </c>
     </row>
     <row r="15">
@@ -4903,9 +5085,11 @@
       <c r="T15" s="2" t="n">
         <v>26.89192646900239</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>76.47780119191297</v>
+      </c>
       <c r="V15" s="2" t="n">
-        <v>5715.242438747673</v>
+        <v>5849.300316241179</v>
       </c>
     </row>
     <row r="16">
@@ -4961,9 +5145,11 @@
       <c r="T16" s="2" t="n">
         <v>13.49617829135049</v>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>28.27997620255626</v>
+      </c>
       <c r="V16" s="2" t="n">
-        <v>79.53245924078773</v>
+        <v>76.95169782704731</v>
       </c>
     </row>
     <row r="17">
@@ -5019,9 +5205,11 @@
       <c r="T17" s="2" t="n">
         <v>119.1536398888879</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>352.8688649082416</v>
+      </c>
       <c r="V17" s="2" t="n">
-        <v>491634.4391305646</v>
+        <v>518378.2638005203</v>
       </c>
     </row>
     <row r="18">
@@ -5077,9 +5265,11 @@
       <c r="T18" s="2" t="n">
         <v>4.77521568509442</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>12.26305011410535</v>
+      </c>
       <c r="V18" s="2" t="n">
-        <v>365799.4279695387</v>
+        <v>368049.7117824112</v>
       </c>
     </row>
     <row r="19">
@@ -5135,9 +5325,11 @@
       <c r="T19" s="2" t="n">
         <v>32.74580900913016</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>88.50426598936681</v>
+      </c>
       <c r="V19" s="2" t="n">
-        <v>9041.886632940366</v>
+        <v>9306.463403563965</v>
       </c>
     </row>
     <row r="20">
@@ -5193,9 +5385,11 @@
       <c r="T20" s="2" t="n">
         <v>8.77424187851827</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>15.20910093043284</v>
+      </c>
       <c r="V20" s="2" t="n">
-        <v>30.61949382134773</v>
+        <v>30.24186607511134</v>
       </c>
     </row>
     <row r="21">
@@ -5251,9 +5445,11 @@
       <c r="T21" s="2" t="n">
         <v>55.9614934730272</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>167.6292882553963</v>
+      </c>
       <c r="V21" s="2" t="n">
-        <v>358.4885016531974</v>
+        <v>355.9925753030737</v>
       </c>
     </row>
     <row r="22">
@@ -5309,9 +5505,11 @@
       <c r="T22" s="2" t="n">
         <v>156.8641762627951</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" s="2" t="n">
+        <v>599.1192070707298</v>
+      </c>
       <c r="V22" s="2" t="n">
-        <v>54263.25630566836</v>
+        <v>54468.06839372768</v>
       </c>
     </row>
     <row r="23">
@@ -5367,9 +5565,11 @@
       <c r="T23" s="2" t="n">
         <v>62.6185180135832</v>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>148.9674428802408</v>
+      </c>
       <c r="V23" s="2" t="n">
-        <v>3599.433765358843</v>
+        <v>3756.974335796574</v>
       </c>
     </row>
     <row r="24">
@@ -5425,9 +5625,11 @@
       <c r="T24" s="2" t="n">
         <v>42.0271777140439</v>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>133.1718490436824</v>
+      </c>
       <c r="V24" s="2" t="n">
-        <v>870.5705143647886</v>
+        <v>873.4544605300705</v>
       </c>
     </row>
     <row r="25">
@@ -5483,9 +5685,11 @@
       <c r="T25" s="2" t="n">
         <v>93.36028271793721</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>238.4009240486365</v>
+      </c>
       <c r="V25" s="2" t="n">
-        <v>1466.805513860761</v>
+        <v>1534.363238304007</v>
       </c>
     </row>
     <row r="26">
@@ -5541,9 +5745,11 @@
       <c r="T26" s="2" t="n">
         <v>64.490704399306</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>167.5412765408897</v>
+      </c>
       <c r="V26" s="2" t="n">
-        <v>2241.303470499185</v>
+        <v>2202.672861758966</v>
       </c>
     </row>
     <row r="27">
@@ -5599,9 +5805,11 @@
       <c r="T27" s="2" t="n">
         <v>35.0656057045034</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>98.54234323175997</v>
+      </c>
       <c r="V27" s="2" t="n">
-        <v>914.7471558289719</v>
+        <v>912.4969484235231</v>
       </c>
     </row>
     <row r="28">
@@ -5657,9 +5865,11 @@
       <c r="T28" s="2" t="n">
         <v>12.98961292613629</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>31.31069154482918</v>
+      </c>
       <c r="V28" s="2" t="n">
-        <v>51.47680407947213</v>
+        <v>52.04538846348984</v>
       </c>
     </row>
     <row r="29">
@@ -5715,9 +5925,11 @@
       <c r="T29" s="2" t="n">
         <v>4.9360974180695</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" s="2" t="n">
+        <v>7.630091079247528</v>
+      </c>
       <c r="V29" s="2" t="n">
-        <v>15.84363644687813</v>
+        <v>15.74045856603944</v>
       </c>
     </row>
     <row r="30">
@@ -5773,9 +5985,11 @@
       <c r="T30" s="2" t="n">
         <v>36.2010618156066</v>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>102.1369852454005</v>
+      </c>
       <c r="V30" s="2" t="n">
-        <v>973.8168227278527</v>
+        <v>1052.784035982254</v>
       </c>
     </row>
     <row r="31">
@@ -5831,9 +6045,11 @@
       <c r="T31" s="2" t="n">
         <v>18.47332305895662</v>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" s="2" t="n">
+        <v>36.84655324199916</v>
+      </c>
       <c r="V31" s="2" t="n">
-        <v>257.2314406079555</v>
+        <v>264.6352371056698</v>
       </c>
     </row>
     <row r="32">
@@ -5889,9 +6105,11 @@
       <c r="T32" s="2" t="n">
         <v>11.26831373991057</v>
       </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="2" t="n">
+        <v>23.33269092207058</v>
+      </c>
       <c r="V32" s="2" t="n">
-        <v>49.44234709626252</v>
+        <v>49.22352449576737</v>
       </c>
     </row>
     <row r="33">
@@ -5947,9 +6165,11 @@
       <c r="T33" s="2" t="n">
         <v>13.95820929634474</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>30.61064370997191</v>
+      </c>
       <c r="V33" s="2" t="n">
-        <v>55.21649223390927</v>
+        <v>54.37521282713333</v>
       </c>
     </row>
     <row r="34">
@@ -6005,7 +6225,9 @@
       <c r="T34" s="2" t="n">
         <v>-4.16928100533256e-14</v>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V34" s="2" t="n">
         <v>0</v>
       </c>
@@ -6063,9 +6285,11 @@
       <c r="T35" s="2" t="n">
         <v>6.02271404967469</v>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>16.75589838390295</v>
+      </c>
       <c r="V35" s="2" t="n">
-        <v>434511.4558208574</v>
+        <v>432377.2805293642</v>
       </c>
     </row>
     <row r="36">
@@ -6121,9 +6345,11 @@
       <c r="T36" s="2" t="n">
         <v>7.53914311447836</v>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>18.96114406377533</v>
+      </c>
       <c r="V36" s="2" t="n">
-        <v>34.58797955858259</v>
+        <v>34.44567748145593</v>
       </c>
     </row>
     <row r="37">
@@ -6179,9 +6405,11 @@
       <c r="T37" s="2" t="n">
         <v>2.882483214733592</v>
       </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>3.486710728595533</v>
+      </c>
       <c r="V37" s="2" t="n">
-        <v>6.806530774155014</v>
+        <v>6.798716360355339</v>
       </c>
     </row>
     <row r="38">
@@ -6237,9 +6465,11 @@
       <c r="T38" s="2" t="n">
         <v>2.612926136363628</v>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>4.040013778726465</v>
+      </c>
       <c r="V38" s="2" t="n">
-        <v>6.748256808111043</v>
+        <v>6.701891479903765</v>
       </c>
     </row>
     <row r="39">
@@ -6295,9 +6525,11 @@
       <c r="T39" s="2" t="n">
         <v>2.909090909090905</v>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>3.255879985173817</v>
+      </c>
       <c r="V39" s="2" t="n">
-        <v>7.614973097363993</v>
+        <v>7.435466290384134</v>
       </c>
     </row>
     <row r="40">
@@ -6353,7 +6585,9 @@
       <c r="T40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V40" s="2" t="n">
         <v>1</v>
       </c>
@@ -6411,7 +6645,9 @@
       <c r="T41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V41" s="2" t="n">
         <v>1</v>
       </c>
@@ -6623,7 +6859,9 @@
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
       </c>
@@ -6687,7 +6925,9 @@
       <c r="T3" s="2" t="n">
         <v>11.45573268643595</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>96.79725031481013</v>
+      </c>
       <c r="V3" s="2" t="n">
         <v>0</v>
       </c>
@@ -6751,9 +6991,11 @@
       <c r="T4" s="2" t="n">
         <v>11.45573268643596</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>31.99787761378754</v>
+      </c>
       <c r="V4" s="2" t="n">
-        <v>0.3042852088602726</v>
+        <v>0.3042852088602723</v>
       </c>
     </row>
     <row r="5">
@@ -6815,7 +7057,9 @@
       <c r="T5" s="2" t="n">
         <v>11.45573268643596</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
       </c>
@@ -6879,7 +7123,9 @@
       <c r="T6" s="2" t="n">
         <v>11.455732686436</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>70.93194274175305</v>
+      </c>
       <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
@@ -6943,7 +7189,9 @@
       <c r="T7" s="2" t="n">
         <v>589.4330104532831</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>16768.7649463136</v>
+      </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
       </c>
@@ -7007,7 +7255,9 @@
       <c r="T8" s="2" t="n">
         <v>980.7365113181207</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>16121.77397378537</v>
+      </c>
       <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
@@ -7071,7 +7321,9 @@
       <c r="T9" s="2" t="n">
         <v>28180.96214906132</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>738053.459371696</v>
+      </c>
       <c r="V9" s="2" t="n">
         <v>0</v>
       </c>
@@ -7135,7 +7387,9 @@
       <c r="T10" s="2" t="n">
         <v>17085.22524944139</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>336287.4499471319</v>
+      </c>
       <c r="V10" s="2" t="n">
         <v>0</v>
       </c>
@@ -7199,7 +7453,9 @@
       <c r="T11" s="2" t="n">
         <v>79503.20618141702</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>1740473.670358903</v>
+      </c>
       <c r="V11" s="2" t="n">
         <v>0</v>
       </c>
@@ -7263,9 +7519,11 @@
       <c r="T12" s="2" t="n">
         <v>1204.974224328892</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>32225.77357871431</v>
+      </c>
       <c r="V12" s="2" t="n">
-        <v>8719.621807822547</v>
+        <v>9364.462679720415</v>
       </c>
     </row>
     <row r="13">
@@ -7327,9 +7585,11 @@
       <c r="T13" s="2" t="n">
         <v>513.2343895775091</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>6525.407273657614</v>
+      </c>
       <c r="V13" s="2" t="n">
-        <v>58.7795138381428</v>
+        <v>57.97407860326917</v>
       </c>
     </row>
     <row r="14">
@@ -7391,9 +7651,11 @@
       <c r="T14" s="2" t="n">
         <v>126.3294177567451</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>1663.634074822245</v>
+      </c>
       <c r="V14" s="2" t="n">
-        <v>120.6555955779325</v>
+        <v>122.7283630538291</v>
       </c>
     </row>
     <row r="15">
@@ -7455,9 +7717,11 @@
       <c r="T15" s="2" t="n">
         <v>467.1943300954471</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>8372.087825950925</v>
+      </c>
       <c r="V15" s="2" t="n">
-        <v>5715.242438747673</v>
+        <v>5849.300316241179</v>
       </c>
     </row>
     <row r="16">
@@ -7519,9 +7783,11 @@
       <c r="T16" s="2" t="n">
         <v>411.5163744177383</v>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>4936.646120944995</v>
+      </c>
       <c r="V16" s="2" t="n">
-        <v>79.53245924078773</v>
+        <v>76.95169782704731</v>
       </c>
     </row>
     <row r="17">
@@ -7583,9 +7849,11 @@
       <c r="T17" s="2" t="n">
         <v>1438.417912447886</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>28202.91345216605</v>
+      </c>
       <c r="V17" s="2" t="n">
-        <v>491634.4391305646</v>
+        <v>518378.2638005203</v>
       </c>
     </row>
     <row r="18">
@@ -7647,9 +7915,11 @@
       <c r="T18" s="2" t="n">
         <v>144.8466506925902</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>2135.61323675179</v>
+      </c>
       <c r="V18" s="2" t="n">
-        <v>365799.4279695387</v>
+        <v>368049.7117824112</v>
       </c>
     </row>
     <row r="19">
@@ -7711,9 +7981,11 @@
       <c r="T19" s="2" t="n">
         <v>574.3013206749507</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>8947.059362770606</v>
+      </c>
       <c r="V19" s="2" t="n">
-        <v>9041.886632940366</v>
+        <v>9306.463403563965</v>
       </c>
     </row>
     <row r="20">
@@ -7775,9 +8047,11 @@
       <c r="T20" s="2" t="n">
         <v>31.78984884432928</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>429.7138297209178</v>
+      </c>
       <c r="V20" s="2" t="n">
-        <v>30.61949382134773</v>
+        <v>30.24186607511134</v>
       </c>
     </row>
     <row r="21">
@@ -7839,9 +8113,11 @@
       <c r="T21" s="2" t="n">
         <v>1026.949166151766</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>19457.93966196803</v>
+      </c>
       <c r="V21" s="2" t="n">
-        <v>358.4885016531974</v>
+        <v>355.9925753030737</v>
       </c>
     </row>
     <row r="22">
@@ -7903,9 +8179,11 @@
       <c r="T22" s="2" t="n">
         <v>1402.543334729835</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" s="2" t="n">
+        <v>36628.01043177136</v>
+      </c>
       <c r="V22" s="2" t="n">
-        <v>54263.25630566836</v>
+        <v>54468.06839372768</v>
       </c>
     </row>
     <row r="23">
@@ -7967,9 +8245,11 @@
       <c r="T23" s="2" t="n">
         <v>386.5475898419766</v>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>7192.0799722064</v>
+      </c>
       <c r="V23" s="2" t="n">
-        <v>3599.433765358843</v>
+        <v>3756.974335796574</v>
       </c>
     </row>
     <row r="24">
@@ -8031,9 +8311,11 @@
       <c r="T24" s="2" t="n">
         <v>302.0977274593374</v>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>6468.171903120117</v>
+      </c>
       <c r="V24" s="2" t="n">
-        <v>870.5705143647886</v>
+        <v>873.4544605300705</v>
       </c>
     </row>
     <row r="25">
@@ -8095,9 +8377,11 @@
       <c r="T25" s="2" t="n">
         <v>498.989545697963</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>10482.76470212062</v>
+      </c>
       <c r="V25" s="2" t="n">
-        <v>1466.805513860761</v>
+        <v>1534.363238304007</v>
       </c>
     </row>
     <row r="26">
@@ -8159,9 +8443,11 @@
       <c r="T26" s="2" t="n">
         <v>365.7817877867718</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>7302.41397314856</v>
+      </c>
       <c r="V26" s="2" t="n">
-        <v>2241.303470499185</v>
+        <v>2202.672861758966</v>
       </c>
     </row>
     <row r="27">
@@ -8223,9 +8509,11 @@
       <c r="T27" s="2" t="n">
         <v>214.8456254500286</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>4639.367520250014</v>
+      </c>
       <c r="V27" s="2" t="n">
-        <v>914.7471558289719</v>
+        <v>912.4969484235231</v>
       </c>
     </row>
     <row r="28">
@@ -8287,9 +8575,11 @@
       <c r="T28" s="2" t="n">
         <v>58.57130611921327</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>1241.732501053916</v>
+      </c>
       <c r="V28" s="2" t="n">
-        <v>51.47680407947213</v>
+        <v>52.04538846348984</v>
       </c>
     </row>
     <row r="29">
@@ -8351,9 +8641,11 @@
       <c r="T29" s="2" t="n">
         <v>33.96434110595385</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" s="2" t="n">
+        <v>384.2199552505144</v>
+      </c>
       <c r="V29" s="2" t="n">
-        <v>15.84363644687813</v>
+        <v>15.74045856603944</v>
       </c>
     </row>
     <row r="30">
@@ -8415,9 +8707,11 @@
       <c r="T30" s="2" t="n">
         <v>238.5392806846162</v>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>5890.540991774528</v>
+      </c>
       <c r="V30" s="2" t="n">
-        <v>973.8168227278527</v>
+        <v>1052.784035982254</v>
       </c>
     </row>
     <row r="31">
@@ -8479,9 +8773,11 @@
       <c r="T31" s="2" t="n">
         <v>124.4227433922786</v>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" s="2" t="n">
+        <v>2077.93919423726</v>
+      </c>
       <c r="V31" s="2" t="n">
-        <v>257.2314406079555</v>
+        <v>264.6352371056698</v>
       </c>
     </row>
     <row r="32">
@@ -8543,9 +8839,11 @@
       <c r="T32" s="2" t="n">
         <v>62.51182103670719</v>
       </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="2" t="n">
+        <v>1076.569235856269</v>
+      </c>
       <c r="V32" s="2" t="n">
-        <v>49.44234709626252</v>
+        <v>49.22352449576737</v>
       </c>
     </row>
     <row r="33">
@@ -8607,9 +8905,11 @@
       <c r="T33" s="2" t="n">
         <v>79.06417419777897</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>1336.899397230146</v>
+      </c>
       <c r="V33" s="2" t="n">
-        <v>55.21649223390927</v>
+        <v>54.37521282713333</v>
       </c>
     </row>
     <row r="34">
@@ -8671,7 +8971,9 @@
       <c r="T34" s="2" t="n">
         <v>93.93701586748909</v>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>928.1296689436963</v>
+      </c>
       <c r="V34" s="2" t="n">
         <v>0</v>
       </c>
@@ -8735,9 +9037,11 @@
       <c r="T35" s="2" t="n">
         <v>37.34627814956497</v>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>804.4519733709429</v>
+      </c>
       <c r="V35" s="2" t="n">
-        <v>434511.4558208574</v>
+        <v>432377.2805293642</v>
       </c>
     </row>
     <row r="36">
@@ -8799,9 +9103,11 @@
       <c r="T36" s="2" t="n">
         <v>49.63422125238045</v>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>913.3481108780538</v>
+      </c>
       <c r="V36" s="2" t="n">
-        <v>34.58797955858259</v>
+        <v>34.44567748145593</v>
       </c>
     </row>
     <row r="37">
@@ -8863,9 +9169,11 @@
       <c r="T37" s="2" t="n">
         <v>20.15498389413338</v>
       </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>201.2434870999223</v>
+      </c>
       <c r="V37" s="2" t="n">
-        <v>6.806530774155014</v>
+        <v>6.798716360355339</v>
       </c>
     </row>
     <row r="38">
@@ -8927,9 +9235,11 @@
       <c r="T38" s="2" t="n">
         <v>13.40149257259501</v>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>172.7076613488797</v>
+      </c>
       <c r="V38" s="2" t="n">
-        <v>6.748256808111043</v>
+        <v>6.701891479903765</v>
       </c>
     </row>
     <row r="39">
@@ -8991,9 +9301,11 @@
       <c r="T39" s="2" t="n">
         <v>38.31771921262021</v>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>343.0664594737765</v>
+      </c>
       <c r="V39" s="2" t="n">
-        <v>7.614973097363993</v>
+        <v>7.435466290384134</v>
       </c>
     </row>
     <row r="40">
@@ -9055,7 +9367,9 @@
       <c r="T40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V40" s="2" t="n">
         <v>1</v>
       </c>
@@ -9119,7 +9433,9 @@
       <c r="T41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V41" s="2" t="n">
         <v>1</v>
       </c>
@@ -9331,7 +9647,9 @@
         <v>1</v>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
@@ -9395,7 +9713,9 @@
       <c r="T3" s="2" t="n">
         <v>11.45573268643595</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>96.79725031481013</v>
+      </c>
       <c r="V3" s="2" t="n">
         <v>0</v>
       </c>
@@ -9459,9 +9779,11 @@
       <c r="T4" s="2" t="n">
         <v>11.45573268643596</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>31.99787761378754</v>
+      </c>
       <c r="V4" s="2" t="n">
-        <v>0.3042852088602726</v>
+        <v>0.3042852088602723</v>
       </c>
     </row>
     <row r="5">
@@ -9523,7 +9845,9 @@
       <c r="T5" s="2" t="n">
         <v>11.45573268643596</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
       </c>
@@ -9587,7 +9911,9 @@
       <c r="T6" s="2" t="n">
         <v>11.455732686436</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>70.93194274175305</v>
+      </c>
       <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
@@ -9651,7 +9977,9 @@
       <c r="T7" s="2" t="n">
         <v>589.4330104533043</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>16768.7649463136</v>
+      </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
       </c>
@@ -9715,7 +10043,9 @@
       <c r="T8" s="2" t="n">
         <v>1159.573909469029</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>16136.27866111681</v>
+      </c>
       <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
@@ -9779,7 +10109,9 @@
       <c r="T9" s="2" t="n">
         <v>28472.38875010574</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>738099.2528492853</v>
+      </c>
       <c r="V9" s="2" t="n">
         <v>0</v>
       </c>
@@ -9843,7 +10175,9 @@
       <c r="T10" s="2" t="n">
         <v>17716.55758727512</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>336357.8280319945</v>
+      </c>
       <c r="V10" s="2" t="n">
         <v>0</v>
       </c>
@@ -9907,7 +10241,9 @@
       <c r="T11" s="2" t="n">
         <v>79829.74122683672</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>1740544.551125968</v>
+      </c>
       <c r="V11" s="2" t="n">
         <v>0</v>
       </c>
@@ -9971,9 +10307,11 @@
       <c r="T12" s="2" t="n">
         <v>1235.005059695206</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>32229.81832902572</v>
+      </c>
       <c r="V12" s="2" t="n">
-        <v>8745.50225642875</v>
+        <v>9391.662138688902</v>
       </c>
     </row>
     <row r="13">
@@ -10035,9 +10373,11 @@
       <c r="T13" s="2" t="n">
         <v>625.6398525504122</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>6535.006357642978</v>
+      </c>
       <c r="V13" s="2" t="n">
-        <v>84.84143089963365</v>
+        <v>84.26381301195687</v>
       </c>
     </row>
     <row r="14">
@@ -10099,9 +10439,11 @@
       <c r="T14" s="2" t="n">
         <v>136.6055189414853</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>1664.508704060671</v>
+      </c>
       <c r="V14" s="2" t="n">
-        <v>124.5851469868333</v>
+        <v>126.7677064564085</v>
       </c>
     </row>
     <row r="15">
@@ -10163,9 +10505,11 @@
       <c r="T15" s="2" t="n">
         <v>549.444451049417</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>8379.75005549382</v>
+      </c>
       <c r="V15" s="2" t="n">
-        <v>5737.693488981377</v>
+        <v>5872.867165714218</v>
       </c>
     </row>
     <row r="16">
@@ -10227,9 +10571,11 @@
       <c r="T16" s="2" t="n">
         <v>495.1925234658902</v>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>4943.256155546237</v>
+      </c>
       <c r="V16" s="2" t="n">
-        <v>97.89018675463855</v>
+        <v>95.42795852018388</v>
       </c>
     </row>
     <row r="17">
@@ -10291,9 +10637,11 @@
       <c r="T17" s="2" t="n">
         <v>1638.427424642126</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>28224.76191993072</v>
+      </c>
       <c r="V17" s="2" t="n">
-        <v>501070.8445438638</v>
+        <v>528322.7833985733</v>
       </c>
     </row>
     <row r="18">
@@ -10355,9 +10703,11 @@
       <c r="T18" s="2" t="n">
         <v>173.9685924898981</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>2138.179836778507</v>
+      </c>
       <c r="V18" s="2" t="n">
-        <v>365808.4816779341</v>
+        <v>368059.0505787696</v>
       </c>
     </row>
     <row r="19">
@@ -10419,9 +10769,11 @@
       <c r="T19" s="2" t="n">
         <v>673.4293131078545</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>8955.769671676242</v>
+      </c>
       <c r="V19" s="2" t="n">
-        <v>9104.502390041736</v>
+        <v>9372.190554609972</v>
       </c>
     </row>
     <row r="20">
@@ -10483,9 +10835,11 @@
       <c r="T20" s="2" t="n">
         <v>31.78984884432919</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>429.7138297209178</v>
+      </c>
       <c r="V20" s="2" t="n">
-        <v>30.61949382134773</v>
+        <v>30.24186607511134</v>
       </c>
     </row>
     <row r="21">
@@ -10547,9 +10901,11 @@
       <c r="T21" s="2" t="n">
         <v>1204.59770274904</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>19477.73428974959</v>
+      </c>
       <c r="V21" s="2" t="n">
-        <v>405.7311300126785</v>
+        <v>404.581424731353</v>
       </c>
     </row>
     <row r="22">
@@ -10611,9 +10967,11 @@
       <c r="T22" s="2" t="n">
         <v>1541.376378024101</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" s="2" t="n">
+        <v>36646.10699017055</v>
+      </c>
       <c r="V22" s="2" t="n">
-        <v>54323.49203517471</v>
+        <v>54529.85719269228</v>
       </c>
     </row>
     <row r="23">
@@ -10675,9 +11033,11 @@
       <c r="T23" s="2" t="n">
         <v>402.7419296743773</v>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>7193.837765876404</v>
+      </c>
       <c r="V23" s="2" t="n">
-        <v>3637.910840168317</v>
+        <v>3797.612340999315</v>
       </c>
     </row>
     <row r="24">
@@ -10739,9 +11099,11 @@
       <c r="T24" s="2" t="n">
         <v>320.873839433629</v>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>6470.309337943433</v>
+      </c>
       <c r="V24" s="2" t="n">
-        <v>877.1168870485229</v>
+        <v>879.9238041237845</v>
       </c>
     </row>
     <row r="25">
@@ -10803,9 +11165,11 @@
       <c r="T25" s="2" t="n">
         <v>503.8815306468321</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>10483.56369063844</v>
+      </c>
       <c r="V25" s="2" t="n">
-        <v>1469.329582827618</v>
+        <v>1536.980813788296</v>
       </c>
     </row>
     <row r="26">
@@ -10867,9 +11231,11 @@
       <c r="T26" s="2" t="n">
         <v>369.116222572059</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>7302.838698035887</v>
+      </c>
       <c r="V26" s="2" t="n">
-        <v>2244.781283997163</v>
+        <v>2206.173007621883</v>
       </c>
     </row>
     <row r="27">
@@ -10931,9 +11297,11 @@
       <c r="T27" s="2" t="n">
         <v>217.2875903163548</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>4639.642195872154</v>
+      </c>
       <c r="V27" s="2" t="n">
-        <v>916.7013995854682</v>
+        <v>914.4877172888382</v>
       </c>
     </row>
     <row r="28">
@@ -10995,9 +11363,11 @@
       <c r="T28" s="2" t="n">
         <v>61.65400644127671</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>1242.265248765626</v>
+      </c>
       <c r="V28" s="2" t="n">
-        <v>52.02426211536708</v>
+        <v>52.60220453997403</v>
       </c>
     </row>
     <row r="29">
@@ -11059,9 +11429,11 @@
       <c r="T29" s="2" t="n">
         <v>37.73815678440172</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" s="2" t="n">
+        <v>384.4560615417278</v>
+      </c>
       <c r="V29" s="2" t="n">
-        <v>16.09268302089474</v>
+        <v>15.98764928155265</v>
       </c>
     </row>
     <row r="30">
@@ -11123,9 +11495,11 @@
       <c r="T30" s="2" t="n">
         <v>241.8699624447206</v>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>5891.013992800264</v>
+      </c>
       <c r="V30" s="2" t="n">
-        <v>975.6572812760189</v>
+        <v>1054.680271904452</v>
       </c>
     </row>
     <row r="31">
@@ -11187,9 +11561,11 @@
       <c r="T31" s="2" t="n">
         <v>124.422743392304</v>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" s="2" t="n">
+        <v>2077.93919423726</v>
+      </c>
       <c r="V31" s="2" t="n">
-        <v>257.2314406079555</v>
+        <v>264.6352371056698</v>
       </c>
     </row>
     <row r="32">
@@ -11251,9 +11627,11 @@
       <c r="T32" s="2" t="n">
         <v>62.51182105004475</v>
       </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="2" t="n">
+        <v>1076.569235856269</v>
+      </c>
       <c r="V32" s="2" t="n">
-        <v>49.44234709626252</v>
+        <v>49.22352449576737</v>
       </c>
     </row>
     <row r="33">
@@ -11315,9 +11693,11 @@
       <c r="T33" s="2" t="n">
         <v>79.06417419779746</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>1336.899397230146</v>
+      </c>
       <c r="V33" s="2" t="n">
-        <v>55.21649223390927</v>
+        <v>54.37521282713333</v>
       </c>
     </row>
     <row r="34">
@@ -11379,9 +11759,11 @@
       <c r="T34" s="2" t="n">
         <v>116.6919459632657</v>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>929.6229819684345</v>
+      </c>
       <c r="V34" s="2" t="n">
-        <v>3.014062032192841</v>
+        <v>3.093012786806117</v>
       </c>
     </row>
     <row r="35">
@@ -11443,9 +11825,11 @@
       <c r="T35" s="2" t="n">
         <v>37.34627814956625</v>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>804.4519733709429</v>
+      </c>
       <c r="V35" s="2" t="n">
-        <v>434511.4558208574</v>
+        <v>432377.2805293642</v>
       </c>
     </row>
     <row r="36">
@@ -11507,9 +11891,11 @@
       <c r="T36" s="2" t="n">
         <v>49.63422125238241</v>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>913.3481108780538</v>
+      </c>
       <c r="V36" s="2" t="n">
-        <v>34.58797955858259</v>
+        <v>34.44567748145593</v>
       </c>
     </row>
     <row r="37">
@@ -11571,9 +11957,11 @@
       <c r="T37" s="2" t="n">
         <v>20.1549838941379</v>
       </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>201.2434870999223</v>
+      </c>
       <c r="V37" s="2" t="n">
-        <v>6.806530774155014</v>
+        <v>6.798716360355339</v>
       </c>
     </row>
     <row r="38">
@@ -11635,9 +12023,11 @@
       <c r="T38" s="2" t="n">
         <v>13.40149257259495</v>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>172.7076613488797</v>
+      </c>
       <c r="V38" s="2" t="n">
-        <v>6.748256808111043</v>
+        <v>6.701891479903765</v>
       </c>
     </row>
     <row r="39">
@@ -11699,9 +12089,11 @@
       <c r="T39" s="2" t="n">
         <v>38.31771921262021</v>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>343.0664594737765</v>
+      </c>
       <c r="V39" s="2" t="n">
-        <v>7.614973097363993</v>
+        <v>7.435466290384134</v>
       </c>
     </row>
     <row r="40">
@@ -11763,7 +12155,9 @@
       <c r="T40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V40" s="2" t="n">
         <v>1</v>
       </c>
@@ -11827,7 +12221,9 @@
       <c r="T41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="V41" s="2" t="n">
         <v>1</v>
       </c>
@@ -13302,22 +13698,22 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0</v>
+        <v>66472.83403682434</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>66462.18629421291</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>1378.874116073328</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>11273.05644750595</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>5.895666947442368</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>0.1223159062933984</v>
       </c>
     </row>
     <row r="21">
@@ -13327,22 +13723,22 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>10026.22286351984</v>
+        <v>10064.06728186468</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9989.881880885045</v>
+        <v>10027.19170922459</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9989.881880885045</v>
+        <v>10027.19170922459</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>11273.05644750595</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8861733219738471</v>
+        <v>0.8894829681654792</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.8861733219738471</v>
+        <v>0.8894829681654792</v>
       </c>
     </row>
   </sheetData>
@@ -13418,25 +13814,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="3">
@@ -13446,10 +13842,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -13645,7 +14041,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -13662,7 +14058,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/PPREstimation/output/top10/13_2_Northern_Humboldt_Current_(1995-1998).xlsx
+++ b/PPREstimation/output/top10/13_2_Northern_Humboldt_Current_(1995-1998).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -4125,7 +4124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4263,6 +4262,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4273,9 +4282,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -4306,19 +4312,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4331,9 +4337,6 @@
           <t>Benthic detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -4364,11 +4367,9 @@
       <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" s="2" t="n">
         <v>0</v>
       </c>
@@ -4379,6 +4380,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4391,9 +4395,6 @@
           <t>Pelagic detritus</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
@@ -4424,11 +4425,9 @@
       <c r="O4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" s="2" t="n">
         <v>0</v>
       </c>
@@ -4439,6 +4438,9 @@
         <v>0</v>
       </c>
       <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4451,9 +4453,6 @@
           <t>Fishery offal</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
@@ -4484,11 +4483,9 @@
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" s="2" t="n">
         <v>0</v>
       </c>
@@ -4499,6 +4496,9 @@
         <v>0</v>
       </c>
       <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4511,9 +4511,6 @@
           <t>Anchovy eggs</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
@@ -4544,11 +4541,9 @@
       <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" s="2" t="n">
         <v>0</v>
       </c>
@@ -4559,6 +4554,9 @@
         <v>0</v>
       </c>
       <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4571,11 +4569,8 @@
           <t>Leatherback turtle</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>1420.917797532486</v>
+        <v>70.9431703745373</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -4583,7 +4578,6 @@
       <c r="H7" s="2" t="n">
         <v>164211.6910817329</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" s="2" t="n">
         <v>0</v>
       </c>
@@ -4602,11 +4596,9 @@
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" s="2" t="n">
         <v>380.773355228876</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" s="2" t="n">
         <v>93.3598933783298</v>
       </c>
@@ -4618,6 +4610,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1420.917797532485</v>
       </c>
     </row>
     <row r="8">
@@ -4629,11 +4624,8 @@
           <t>Green sea turtle</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>659.7533275876393</v>
+        <v>32.2629340729456</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
@@ -4641,7 +4633,6 @@
       <c r="H8" s="2" t="n">
         <v>91773.17765722508</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" s="2" t="n">
         <v>0</v>
       </c>
@@ -4660,11 +4651,9 @@
       <c r="O8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" s="2" t="n">
         <v>155.8532447422448</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" s="2" t="n">
         <v>38.9436369956886</v>
       </c>
@@ -4676,6 +4665,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>659.753327587639</v>
       </c>
     </row>
     <row r="9">
@@ -4687,11 +4679,8 @@
           <t>Cetaceans</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>4283.740146857348</v>
+        <v>121.1794672014966</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -4699,7 +4688,6 @@
       <c r="H9" s="2" t="n">
         <v>364.9523727117391</v>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" s="2" t="n">
         <v>0</v>
       </c>
@@ -4718,11 +4706,9 @@
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" s="2" t="n">
         <v>21171.8043507299</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" s="2" t="n">
         <v>4662.88804661625</v>
       </c>
@@ -4734,6 +4720,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4283.740146857345</v>
       </c>
     </row>
     <row r="10">
@@ -4745,11 +4734,8 @@
           <t>Pinnipeds</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>990.6708478713258</v>
+        <v>56.04309988809577</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4743,6 @@
       <c r="H10" s="2" t="n">
         <v>48.4448489635823</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" s="2" t="n">
         <v>0</v>
       </c>
@@ -4776,11 +4761,9 @@
       <c r="O10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" s="2" t="n">
         <v>10248.56433798751</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" s="2" t="n">
         <v>2978.011516594248</v>
       </c>
@@ -4792,6 +4775,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>990.6708478713253</v>
       </c>
     </row>
     <row r="11">
@@ -4803,11 +4789,8 @@
           <t>Seabirds</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>1120.017624108959</v>
+        <v>64.70480623005056</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -4815,7 +4798,6 @@
       <c r="H11" s="2" t="n">
         <v>29.45607295193398</v>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" s="2" t="n">
         <v>0</v>
       </c>
@@ -4834,11 +4816,9 @@
       <c r="O11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" s="2" t="n">
         <v>50841.0402540028</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" s="2" t="n">
         <v>14683.2434683836</v>
       </c>
@@ -4850,6 +4830,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1120.017624108958</v>
       </c>
     </row>
     <row r="12">
@@ -4861,11 +4844,8 @@
           <t>Chondrichthyans</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>6361.615187051841</v>
+        <v>159.8175533438862</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2595.93545863506</v>
@@ -4894,11 +4874,9 @@
       <c r="O12" s="2" t="n">
         <v>7571.338584891741</v>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" s="2" t="n">
         <v>897.313093642693</v>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" s="2" t="n">
         <v>195.2023860062869</v>
       </c>
@@ -4910,6 +4888,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>9364.462679720415</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6361.615187051837</v>
       </c>
     </row>
     <row r="13">
@@ -4921,11 +4902,8 @@
           <t>Catfish</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>119.4042477003443</v>
+        <v>7.545737595489292</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>22.09876996861382</v>
@@ -4954,11 +4932,9 @@
       <c r="O13" s="2" t="n">
         <v>50.27321386920971</v>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" s="2" t="n">
         <v>27.93755951797638</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" s="2" t="n">
         <v>8.15664640356176</v>
       </c>
@@ -4970,6 +4946,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>57.97407860326917</v>
+      </c>
+      <c r="X13" t="n">
+        <v>119.4042477003442</v>
       </c>
     </row>
     <row r="14">
@@ -4981,11 +4960,8 @@
           <t>Sea robin</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>225.0734185528845</v>
+        <v>21.90333865877085</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>61.7672492925663</v>
@@ -5014,11 +4990,9 @@
       <c r="O14" s="2" t="n">
         <v>106.8741859781986</v>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" s="2" t="n">
         <v>40.042364752721</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" s="2" t="n">
         <v>14.80448689328224</v>
       </c>
@@ -5030,6 +5004,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>122.7283630538291</v>
+      </c>
+      <c r="X14" t="n">
+        <v>225.0734185528844</v>
       </c>
     </row>
     <row r="15">
@@ -5041,11 +5018,8 @@
           <t>Medium sciaenids</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>427.6480819623888</v>
+        <v>23.99494695117952</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>2295.205121889212</v>
@@ -5074,11 +5048,9 @@
       <c r="O15" s="2" t="n">
         <v>4929.78853768923</v>
       </c>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" s="2" t="n">
         <v>90.43516740793009</v>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" s="2" t="n">
         <v>26.89192647208725</v>
       </c>
@@ -5090,6 +5062,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>5849.300316241179</v>
+      </c>
+      <c r="X15" t="n">
+        <v>427.6480819623886</v>
       </c>
     </row>
     <row r="16">
@@ -5101,11 +5076,8 @@
           <t>Medium demersal fish</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>193.7278593553508</v>
+        <v>13.64298978894894</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>35.8393206730202</v>
@@ -5134,11 +5106,9 @@
       <c r="O16" s="2" t="n">
         <v>68.1994924487126</v>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" s="2" t="n">
         <v>38.4963044139472</v>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" s="2" t="n">
         <v>13.49617829226943</v>
       </c>
@@ -5150,6 +5120,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>76.95169782704731</v>
+      </c>
+      <c r="X16" t="n">
+        <v>193.7278593553507</v>
       </c>
     </row>
     <row r="17">
@@ -5161,11 +5134,8 @@
           <t>Conger</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>3718.814105276248</v>
+        <v>100.7308911445894</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>242808.9717571305</v>
@@ -5194,11 +5164,9 @@
       <c r="O17" s="2" t="n">
         <v>438349.590428255</v>
       </c>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" s="2" t="n">
         <v>462.587543131279</v>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" s="2" t="n">
         <v>119.1536398966884</v>
       </c>
@@ -5210,6 +5178,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>518378.2638005203</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3718.814105276247</v>
       </c>
     </row>
     <row r="18">
@@ -5221,11 +5192,8 @@
           <t>Butter fishes</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>156.4588208938396</v>
+        <v>10.1629911720568</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>183534.9409112841</v>
@@ -5254,11 +5222,9 @@
       <c r="O18" s="2" t="n">
         <v>319777.862778925</v>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" s="2" t="n">
         <v>13.2870892407835</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" s="2" t="n">
         <v>4.77521568509434</v>
       </c>
@@ -5270,6 +5236,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>368049.7117824112</v>
+      </c>
+      <c r="X18" t="n">
+        <v>156.4588208938396</v>
       </c>
     </row>
     <row r="19">
@@ -5281,11 +5250,8 @@
           <t>Benthic elasmobranchs</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>901.535002468944</v>
+        <v>31.67094808761469</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4353.901137517046</v>
@@ -5314,11 +5280,9 @@
       <c r="O19" s="2" t="n">
         <v>7895.72416321221</v>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" s="2" t="n">
         <v>121.9439362124481</v>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" s="2" t="n">
         <v>32.74580901188884</v>
       </c>
@@ -5330,6 +5294,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>9306.463403563965</v>
+      </c>
+      <c r="X19" t="n">
+        <v>901.5350024689435</v>
       </c>
     </row>
     <row r="20">
@@ -5341,11 +5308,8 @@
           <t>Small demersal fish</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>59.94336938619239</v>
+        <v>10.01560312188686</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>19.03636195942525</v>
@@ -5374,11 +5338,9 @@
       <c r="O20" s="2" t="n">
         <v>27.46092768324986</v>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" s="2" t="n">
         <v>17.7499988960181</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" s="2" t="n">
         <v>8.774241878518321</v>
       </c>
@@ -5390,6 +5352,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>30.24186607511134</v>
+      </c>
+      <c r="X20" t="n">
+        <v>59.94336938619238</v>
       </c>
     </row>
     <row r="21">
@@ -5401,11 +5366,8 @@
           <t>Flatfish</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>1232.203699897848</v>
+        <v>52.62926921604958</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>172.1182082820299</v>
@@ -5434,11 +5396,9 @@
       <c r="O21" s="2" t="n">
         <v>310.6668084679349</v>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" s="2" t="n">
         <v>194.9146671900978</v>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" s="2" t="n">
         <v>55.9614934817029</v>
       </c>
@@ -5450,6 +5410,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>355.9925753030737</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1232.203699897847</v>
       </c>
     </row>
     <row r="22">
@@ -5461,11 +5424,8 @@
           <t>Large hake</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>6008.193485244471</v>
+        <v>140.5192169443272</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>25638.09824378347</v>
@@ -5494,11 +5454,9 @@
       <c r="O22" s="2" t="n">
         <v>46949.7314258816</v>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" s="2" t="n">
         <v>758.739752574152</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" s="2" t="n">
         <v>156.8641762739691</v>
       </c>
@@ -5510,6 +5468,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>54468.06839372768</v>
+      </c>
+      <c r="X22" t="n">
+        <v>6008.193485244467</v>
       </c>
     </row>
     <row r="23">
@@ -5521,11 +5482,8 @@
           <t>Medium hake</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>1150.053722170485</v>
+        <v>61.6339776013052</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1771.707898742737</v>
@@ -5554,11 +5512,9 @@
       <c r="O23" s="2" t="n">
         <v>3199.076524260398</v>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" s="2" t="n">
         <v>207.2657765439532</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" s="2" t="n">
         <v>62.6185180186049</v>
       </c>
@@ -5570,6 +5526,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>3756.974335796574</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1150.053722170485</v>
       </c>
     </row>
     <row r="24">
@@ -5581,11 +5540,8 @@
           <t>Small hake</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>1080.940718261372</v>
+        <v>52.47626368179917</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>288.7615237091754</v>
@@ -5614,11 +5570,9 @@
       <c r="O24" s="2" t="n">
         <v>725.7051763180179</v>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" s="2" t="n">
         <v>182.1555691863234</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" s="2" t="n">
         <v>42.0271777166842</v>
       </c>
@@ -5630,6 +5584,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>873.4544605300705</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1080.940718261371</v>
       </c>
     </row>
     <row r="25">
@@ -5641,11 +5598,8 @@
           <t>Other large pelagic fish</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>1271.535269541561</v>
+        <v>65.39744156038532</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>553.8114083771081</v>
@@ -5674,11 +5628,9 @@
       <c r="O25" s="2" t="n">
         <v>1277.756768263261</v>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" s="2" t="n">
         <v>326.2910046860121</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" s="2" t="n">
         <v>93.36028273187681</v>
       </c>
@@ -5690,6 +5642,9 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>1534.363238304007</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1271.53526954156</v>
       </c>
     </row>
     <row r="26">
@@ -5701,11 +5656,8 @@
           <t>Chub mackerel</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>678.0279778074322</v>
+        <v>43.91908230653397</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1141.964575481477</v>
@@ -5734,11 +5686,9 @@
       <c r="O26" s="2" t="n">
         <v>1947.662642989854</v>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" s="2" t="n">
         <v>220.5183865503054</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" s="2" t="n">
         <v>64.49070440850009</v>
       </c>
@@ -5750,6 +5700,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>2202.672861758966</v>
+      </c>
+      <c r="X26" t="n">
+        <v>678.0279778074319</v>
       </c>
     </row>
     <row r="27">
@@ -5761,11 +5714,8 @@
           <t>Horse mackerel</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>602.8487368702999</v>
+        <v>39.00569380007316</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>464.3939981829197</v>
@@ -5794,11 +5744,9 @@
       <c r="O27" s="2" t="n">
         <v>798.0340023153669</v>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" s="2" t="n">
         <v>138.5772356796728</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" s="2" t="n">
         <v>35.0656057097642</v>
       </c>
@@ -5810,6 +5758,9 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>912.4969484235231</v>
+      </c>
+      <c r="X27" t="n">
+        <v>602.8487368702997</v>
       </c>
     </row>
     <row r="28">
@@ -5821,11 +5772,8 @@
           <t>Other small pelagic fish</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>90.84944274542406</v>
+        <v>13.48068833907816</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>30.15863766913503</v>
@@ -5854,11 +5802,9 @@
       <c r="O28" s="2" t="n">
         <v>46.8245148185259</v>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" s="2" t="n">
         <v>36.5156249999996</v>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" s="2" t="n">
         <v>12.9896129261364</v>
       </c>
@@ -5870,6 +5816,9 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>52.04538846348984</v>
+      </c>
+      <c r="X28" t="n">
+        <v>90.84944274542403</v>
       </c>
     </row>
     <row r="29">
@@ -5881,11 +5830,8 @@
           <t>Other cephalopods</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>150.4804052315152</v>
+        <v>18.17310645160368</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>6.999789774229993</v>
@@ -5914,11 +5860,9 @@
       <c r="O29" s="2" t="n">
         <v>13.58206358593469</v>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" s="2" t="n">
         <v>10.92990060468016</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" s="2" t="n">
         <v>4.9360974180671</v>
       </c>
@@ -5930,6 +5874,9 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>15.74045856603944</v>
+      </c>
+      <c r="X29" t="n">
+        <v>150.4804052315151</v>
       </c>
     </row>
     <row r="30">
@@ -5941,11 +5888,8 @@
           <t>Jumbo squid</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>841.3547781217205</v>
+        <v>48.3893320477674</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>175.2605969310956</v>
@@ -5974,11 +5918,9 @@
       <c r="O30" s="2" t="n">
         <v>830.075714722672</v>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" s="2" t="n">
         <v>147.1990102614638</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" s="2" t="n">
         <v>36.2010618164706</v>
       </c>
@@ -5990,6 +5932,9 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>1052.784035982254</v>
+      </c>
+      <c r="X30" t="n">
+        <v>841.3547781217202</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +5946,8 @@
           <t>Mesopelagic fish</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>158.4472892044162</v>
+        <v>19.78459939171336</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>117.7072141819992</v>
@@ -6034,11 +5976,9 @@
       <c r="O31" s="2" t="n">
         <v>225.0866553755816</v>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" s="2" t="n">
         <v>50.9254304469751</v>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" s="2" t="n">
         <v>18.47332305894836</v>
       </c>
@@ -6050,6 +5990,9 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>264.6352371056698</v>
+      </c>
+      <c r="X31" t="n">
+        <v>158.4472892044162</v>
       </c>
     </row>
     <row r="32">
@@ -6061,11 +6004,8 @@
           <t>Anchovy</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>114.1511855892308</v>
+        <v>15.60029820959277</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>25.59666873290363</v>
@@ -6094,11 +6034,9 @@
       <c r="O32" s="2" t="n">
         <v>43.6731753356332</v>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" s="2" t="n">
         <v>30.75706671146475</v>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" s="2" t="n">
         <v>11.2683137425023</v>
       </c>
@@ -6110,6 +6048,9 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>49.22352449576737</v>
+      </c>
+      <c r="X32" t="n">
+        <v>114.1511855892307</v>
       </c>
     </row>
     <row r="33">
@@ -6121,11 +6062,8 @@
           <t>Sardine</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>125.9465124697329</v>
+        <v>17.22643065629575</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>28.27675595386741</v>
@@ -6154,11 +6092,9 @@
       <c r="O33" s="2" t="n">
         <v>48.1539278679718</v>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" s="2" t="n">
         <v>40.1447488119726</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" s="2" t="n">
         <v>13.95820929634301</v>
       </c>
@@ -6170,6 +6106,9 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>54.37521282713333</v>
+      </c>
+      <c r="X33" t="n">
+        <v>125.9465124697328</v>
       </c>
     </row>
     <row r="34">
@@ -6181,9 +6120,6 @@
           <t>Macrobenthos</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
@@ -6214,11 +6150,9 @@
       <c r="O34" s="2" t="n">
         <v>-6.02916332238322e-13</v>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" s="2" t="n">
         <v>-1.273541533442212e-14</v>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" s="2" t="n">
         <v>2.540188060832987e-15</v>
       </c>
@@ -6229,6 +6163,9 @@
         <v>0</v>
       </c>
       <c r="V34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6241,11 +6178,8 @@
           <t>Chrysaora plocamia</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>159.6246450623831</v>
+        <v>18.03177094273526</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>218944.1196765155</v>
@@ -6274,11 +6208,9 @@
       <c r="O35" s="2" t="n">
         <v>381475.864896308</v>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" s="2" t="n">
         <v>19.70552664837089</v>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" s="2" t="n">
         <v>6.0227140496743</v>
       </c>
@@ -6290,6 +6222,9 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>432377.2805293642</v>
+      </c>
+      <c r="X35" t="n">
+        <v>159.6246450623831</v>
       </c>
     </row>
     <row r="36">
@@ -6301,11 +6236,8 @@
           <t>Gelatinous zooplankton</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="n">
-        <v>106.0858937321907</v>
+        <v>14.44472369268337</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>14.40529738510895</v>
@@ -6334,11 +6266,9 @@
       <c r="O36" s="2" t="n">
         <v>30.43362203042686</v>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" s="2" t="n">
         <v>24.43597415709127</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" s="2" t="n">
         <v>7.539143114477739</v>
       </c>
@@ -6350,6 +6280,9 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>34.44567748145593</v>
+      </c>
+      <c r="X36" t="n">
+        <v>106.0858937321906</v>
       </c>
     </row>
     <row r="37">
@@ -6361,11 +6294,8 @@
           <t>Macrozooplankton</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>16.72799329812509</v>
+        <v>4.819349793113476</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>2.998933251834443</v>
@@ -6394,11 +6324,9 @@
       <c r="O37" s="2" t="n">
         <v>5.92546502753431</v>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" s="2" t="n">
         <v>5.08130053879051</v>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" s="2" t="n">
         <v>2.882483214732131</v>
       </c>
@@ -6410,6 +6338,9 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>6.798716360355339</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16.72799329812509</v>
       </c>
     </row>
     <row r="38">
@@ -6421,11 +6352,8 @@
           <t>Mesozooplankton</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>13.9233337608831</v>
+        <v>4.547708681194301</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>3.714272797412857</v>
@@ -6454,11 +6382,9 @@
       <c r="O38" s="2" t="n">
         <v>6.02185572619858</v>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" s="2" t="n">
         <v>5.15624999999996</v>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" s="2" t="n">
         <v>2.612926136363645</v>
       </c>
@@ -6470,6 +6396,9 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>6.701891479903765</v>
+      </c>
+      <c r="X38" t="n">
+        <v>13.9233337608831</v>
       </c>
     </row>
     <row r="39">
@@ -6481,11 +6410,8 @@
           <t>Microzooplankton</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>3.886537782008045</v>
+        <v>1.656098805326215</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>1.672337613574199</v>
@@ -6514,11 +6440,9 @@
       <c r="O39" s="2" t="n">
         <v>6.23187373681345</v>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" s="2" t="n">
         <v>5.3333333333332</v>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" s="2" t="n">
         <v>2.909090909090918</v>
       </c>
@@ -6530,6 +6454,9 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>7.435466290384134</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.886537782008044</v>
       </c>
     </row>
     <row r="40">
@@ -6541,9 +6468,6 @@
           <t>Dino/silicoflagellates</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
@@ -6574,11 +6498,9 @@
       <c r="O40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" s="2" t="n">
         <v>1</v>
       </c>
@@ -6589,6 +6511,9 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6601,9 +6526,6 @@
           <t>Diatoms</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
@@ -6634,11 +6556,9 @@
       <c r="O41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" s="2" t="n">
         <v>1</v>
       </c>
@@ -6649,6 +6569,9 @@
         <v>1</v>
       </c>
       <c r="V41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6663,7 +6586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6801,6 +6724,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6850,19 +6783,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6914,11 +6850,9 @@
       <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" s="2" t="n">
         <v>-4.497969730785198</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" s="2" t="n">
         <v>11.00350975195064</v>
       </c>
@@ -6930,6 +6864,12 @@
       </c>
       <c r="V3" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -6980,11 +6920,9 @@
       <c r="O4" s="2" t="n">
         <v>0.3042852088602729</v>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" s="2" t="n">
         <v>-1.126229271969796</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" s="2" t="n">
         <v>11.00350975195064</v>
       </c>
@@ -6996,6 +6934,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0.3042852088602723</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7046,11 +6990,9 @@
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" s="2" t="n">
         <v>11.00350975195064</v>
       </c>
@@ -7062,6 +7004,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -7112,11 +7060,9 @@
       <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" s="2" t="n">
         <v>-3.070894912027654</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" s="2" t="n">
         <v>11.00350975195065</v>
       </c>
@@ -7128,6 +7074,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -7146,10 +7098,10 @@
         <v>991.1394114273684</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>909.2676876500602</v>
+        <v>70.58197301449189</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2094.892902187049</v>
+        <v>92.56058686811353</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -7178,11 +7130,9 @@
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" s="2" t="n">
         <v>-601.0112173140612</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" s="2" t="n">
         <v>569.8501826354508</v>
       </c>
@@ -7194,6 +7144,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>909.2676876500599</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2094.892902187048</v>
       </c>
     </row>
     <row r="8">
@@ -7212,10 +7168,10 @@
         <v>275.5520862134852</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>256.8669565779018</v>
+        <v>32.03832086819186</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1014.310493310935</v>
+        <v>49.59163384194427</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
@@ -7244,11 +7200,9 @@
       <c r="O8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" s="2" t="n">
         <v>-760.0034117516643</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" s="2" t="n">
         <v>943.5585892270881</v>
       </c>
@@ -7260,6 +7214,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>256.8669565779015</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1014.310493310935</v>
       </c>
     </row>
     <row r="9">
@@ -7278,10 +7238,10 @@
         <v>1347.512651739257</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1231.466989345203</v>
+        <v>85.31078291082535</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6581.070747016191</v>
+        <v>160.3923994246631</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -7310,11 +7270,9 @@
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" s="2" t="n">
         <v>-35058.98412565851</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" s="2" t="n">
         <v>27252.56997984529</v>
       </c>
@@ -7326,6 +7284,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1231.466989345202</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6581.070747016186</v>
       </c>
     </row>
     <row r="10">
@@ -7344,10 +7308,10 @@
         <v>530.1130576685345</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>490.1418699926787</v>
+        <v>47.97410565466274</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1478.869373568349</v>
+        <v>71.34486949900355</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -7376,11 +7340,9 @@
       <c r="O10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" s="2" t="n">
         <v>-16018.28575222339</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" s="2" t="n">
         <v>16528.33327321705</v>
       </c>
@@ -7392,6 +7354,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>490.1418699926785</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1478.869373568349</v>
       </c>
     </row>
     <row r="11">
@@ -7410,10 +7378,10 @@
         <v>791.4867217282414</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>728.1510850960457</v>
+        <v>61.43499302912673</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1674.12745327595</v>
+        <v>82.70860073067109</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -7442,11 +7410,9 @@
       <c r="O11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" s="2" t="n">
         <v>-74288.45811123669</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" s="2" t="n">
         <v>76944.39351658642</v>
       </c>
@@ -7458,6 +7424,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>728.1510850960461</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1674.127453275949</v>
       </c>
     </row>
     <row r="12">
@@ -7476,10 +7448,10 @@
         <v>2800.516288983121</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2536.04895514903</v>
+        <v>133.9789001764712</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>9811.545591632886</v>
+        <v>212.0980393453545</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>3407.596957473355</v>
@@ -7508,11 +7480,9 @@
       <c r="O12" s="2" t="n">
         <v>7571.338584891741</v>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" s="2" t="n">
         <v>-1529.398807410988</v>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" s="2" t="n">
         <v>1165.112785722626</v>
       </c>
@@ -7524,6 +7494,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>9364.462679720415</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2536.048955149029</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9811.545591632881</v>
       </c>
     </row>
     <row r="13">
@@ -7542,10 +7518,10 @@
         <v>117.3184317678517</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>110.5363646963467</v>
+        <v>18.91704521019124</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>241.6221399774824</v>
+        <v>20.90500715161561</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>83.21721105708285</v>
@@ -7574,11 +7550,9 @@
       <c r="O13" s="2" t="n">
         <v>50.27321386920971</v>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" s="2" t="n">
         <v>-386.4307175266204</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" s="2" t="n">
         <v>493.2960979362349</v>
       </c>
@@ -7590,6 +7564,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>57.97407860326917</v>
+      </c>
+      <c r="W13" t="n">
+        <v>110.5363646963466</v>
+      </c>
+      <c r="X13" t="n">
+        <v>241.6221399774823</v>
       </c>
     </row>
     <row r="14">
@@ -7608,10 +7588,10 @@
         <v>190.4081560092463</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>178.3183738036412</v>
+        <v>25.50502949857076</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>350.1967128679919</v>
+        <v>30.58853281259601</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>88.59797157286792</v>
@@ -7640,11 +7620,9 @@
       <c r="O14" s="2" t="n">
         <v>106.8741859781986</v>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" s="2" t="n">
         <v>-89.74396731786661</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" s="2" t="n">
         <v>121.9268943315193</v>
       </c>
@@ -7656,6 +7634,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>122.7283630538291</v>
+      </c>
+      <c r="W14" t="n">
+        <v>178.3183738036411</v>
+      </c>
+      <c r="X14" t="n">
+        <v>350.1967128679917</v>
       </c>
     </row>
     <row r="15">
@@ -7674,10 +7658,10 @@
         <v>206.3558002114387</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>193.0592836509582</v>
+        <v>26.80274388342972</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>683.6403565099511</v>
+        <v>38.54853586342779</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3050.711353739617</v>
@@ -7706,11 +7690,9 @@
       <c r="O15" s="2" t="n">
         <v>4929.78853768923</v>
       </c>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" s="2" t="n">
         <v>-365.686594796515</v>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" s="2" t="n">
         <v>449.8130895692353</v>
       </c>
@@ -7722,6 +7704,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>5849.300316241179</v>
+      </c>
+      <c r="W15" t="n">
+        <v>193.0592836509578</v>
+      </c>
+      <c r="X15" t="n">
+        <v>683.6403565099507</v>
       </c>
     </row>
     <row r="16">
@@ -7740,10 +7728,10 @@
         <v>150.4468635259402</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>141.3097633252641</v>
+        <v>22.05477127058738</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>337.7372597038965</v>
+        <v>26.25286036574757</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>88.13504965389194</v>
@@ -7772,11 +7760,9 @@
       <c r="O16" s="2" t="n">
         <v>68.1994924487126</v>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" s="2" t="n">
         <v>-298.7938205865035</v>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" s="2" t="n">
         <v>395.8042531538186</v>
       </c>
@@ -7788,6 +7774,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>76.95169782704731</v>
+      </c>
+      <c r="W16" t="n">
+        <v>141.309763325264</v>
+      </c>
+      <c r="X16" t="n">
+        <v>337.7372597038964</v>
       </c>
     </row>
     <row r="17">
@@ -7806,10 +7798,10 @@
         <v>1310.103589747261</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1197.700868625728</v>
+        <v>83.84157247118402</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5816.982086870095</v>
+        <v>147.1398792261239</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>332687.4436514152</v>
@@ -7838,11 +7830,9 @@
       <c r="O17" s="2" t="n">
         <v>438349.590428255</v>
       </c>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" s="2" t="n">
         <v>-1387.137485621574</v>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" s="2" t="n">
         <v>1386.339046998091</v>
       </c>
@@ -7854,6 +7844,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>518378.2638005203</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1197.700868625727</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5816.982086870092</v>
       </c>
     </row>
     <row r="18">
@@ -7872,10 +7868,10 @@
         <v>40.75628967116911</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38.9109542065526</v>
+        <v>9.852180611192738</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>254.0626451325671</v>
+        <v>17.52106008093881</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>240515.6852955938</v>
@@ -7904,11 +7900,9 @@
       <c r="O18" s="2" t="n">
         <v>319777.862778925</v>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" s="2" t="n">
         <v>-101.4248259510073</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" s="2" t="n">
         <v>139.3172343636154</v>
       </c>
@@ -7920,6 +7914,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>368049.7117824112</v>
+      </c>
+      <c r="W18" t="n">
+        <v>38.91095420655259</v>
+      </c>
+      <c r="X18" t="n">
+        <v>254.0626451325669</v>
       </c>
     </row>
     <row r="19">
@@ -7938,10 +7938,10 @@
         <v>227.6721074390069</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>212.7405595194875</v>
+        <v>28.47882382785136</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1440.711189763718</v>
+        <v>51.08643174538328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5821.0324841821</v>
@@ -7970,11 +7970,9 @@
       <c r="O19" s="2" t="n">
         <v>7895.72416321221</v>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" s="2" t="n">
         <v>-486.5387426414657</v>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" s="2" t="n">
         <v>552.9230440029817</v>
       </c>
@@ -7986,6 +7984,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>9306.463403563965</v>
+      </c>
+      <c r="W19" t="n">
+        <v>212.7405595194874</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1440.711189763717</v>
       </c>
     </row>
     <row r="20">
@@ -8004,10 +8008,10 @@
         <v>28.84031503126606</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>27.65376308392867</v>
+        <v>7.958996774982072</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>83.33437473728972</v>
+        <v>11.82535459198235</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>22.31942905594573</v>
@@ -8036,11 +8040,9 @@
       <c r="O20" s="2" t="n">
         <v>27.46092768324986</v>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" s="2" t="n">
         <v>-14.11061804876872</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" s="2" t="n">
         <v>30.88129191428204</v>
       </c>
@@ -8052,6 +8054,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>30.24186607511134</v>
+      </c>
+      <c r="W20" t="n">
+        <v>27.65376308392866</v>
+      </c>
+      <c r="X20" t="n">
+        <v>83.33437473728969</v>
       </c>
     </row>
     <row r="21">
@@ -8070,10 +8078,10 @@
         <v>734.4818583377563</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>676.3393077380938</v>
+        <v>58.66587620713965</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2029.750446318654</v>
+        <v>82.73422950318442</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>329.9394788235357</v>
@@ -8102,11 +8110,9 @@
       <c r="O21" s="2" t="n">
         <v>310.6668084679349</v>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" s="2" t="n">
         <v>-921.6445309759478</v>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" s="2" t="n">
         <v>988.6187592485774</v>
       </c>
@@ -8118,6 +8124,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>355.9925753030737</v>
+      </c>
+      <c r="W21" t="n">
+        <v>676.3393077380936</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2029.750446318652</v>
       </c>
     </row>
     <row r="22">
@@ -8136,10 +8148,10 @@
         <v>2043.792593773252</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1858.08667865269</v>
+        <v>110.3129315338512</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>9301.269320536268</v>
+        <v>193.9045133267285</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>33698.40182714671</v>
@@ -8168,11 +8180,9 @@
       <c r="O22" s="2" t="n">
         <v>46949.7314258816</v>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" s="2" t="n">
         <v>-1680.085659887558</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" s="2" t="n">
         <v>1353.369292299113</v>
       </c>
@@ -8184,6 +8194,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>54468.06839372768</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1858.086678652689</v>
+      </c>
+      <c r="X22" t="n">
+        <v>9301.269320536263</v>
       </c>
     </row>
     <row r="23">
@@ -8202,10 +8218,10 @@
         <v>684.9096007862478</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>631.242264454877</v>
+        <v>56.19014597439239</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1740.698250458059</v>
+        <v>80.49420936136312</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>2356.246169973124</v>
@@ -8234,11 +8250,9 @@
       <c r="O23" s="2" t="n">
         <v>3199.076524260398</v>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" s="2" t="n">
         <v>-342.5253690346095</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" s="2" t="n">
         <v>373.7602666945551</v>
       </c>
@@ -8250,6 +8264,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>3756.974335796574</v>
+      </c>
+      <c r="W23" t="n">
+        <v>631.2422644548756</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1740.698250458058</v>
       </c>
     </row>
     <row r="24">
@@ -8268,10 +8288,10 @@
         <v>457.1259612054471</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>423.4412461107</v>
+        <v>43.78365113542493</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1663.434941426748</v>
+        <v>70.47544890258473</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>390.8725997983238</v>
@@ -8300,11 +8320,9 @@
       <c r="O24" s="2" t="n">
         <v>725.7051763180179</v>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" s="2" t="n">
         <v>-343.2045150054447</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" s="2" t="n">
         <v>291.831263447726</v>
       </c>
@@ -8316,6 +8334,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>873.4544605300705</v>
+      </c>
+      <c r="W24" t="n">
+        <v>423.4412461106999</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1663.434941426747</v>
       </c>
     </row>
     <row r="25">
@@ -8334,10 +8358,10 @@
         <v>721.5611730784314</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>664.5888305031265</v>
+        <v>58.02692732730644</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1922.667229416334</v>
+        <v>83.89223638542532</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>706.388690585876</v>
@@ -8366,11 +8390,9 @@
       <c r="O25" s="2" t="n">
         <v>1277.756768263261</v>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" s="2" t="n">
         <v>-480.6291832557359</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" s="2" t="n">
         <v>482.9770512085926</v>
       </c>
@@ -8382,6 +8404,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>1534.363238304007</v>
+      </c>
+      <c r="W25" t="n">
+        <v>664.5888305031262</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1922.667229416333</v>
       </c>
     </row>
     <row r="26">
@@ -8400,10 +8428,10 @@
         <v>367.1023673046354</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>340.9846193549697</v>
+        <v>38.24203771105975</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1025.940036514624</v>
+        <v>57.02922481792493</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1459.778971141264</v>
@@ -8432,11 +8460,9 @@
       <c r="O26" s="2" t="n">
         <v>1947.662642989854</v>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" s="2" t="n">
         <v>-337.7853368908898</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" s="2" t="n">
         <v>353.8881147948119</v>
       </c>
@@ -8448,6 +8474,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>2202.672861758966</v>
+      </c>
+      <c r="W26" t="n">
+        <v>340.9846193549695</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1025.940036514623</v>
       </c>
     </row>
     <row r="27">
@@ -8466,10 +8498,10 @@
         <v>256.9728150281728</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>239.7566088528666</v>
+        <v>30.68765174730518</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>916.6652623431332</v>
+        <v>51.53889402961849</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>602.7515782195904</v>
@@ -8498,11 +8530,9 @@
       <c r="O27" s="2" t="n">
         <v>798.0340023153669</v>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" s="2" t="n">
         <v>-225.3563962676403</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" s="2" t="n">
         <v>207.7486853715936</v>
       </c>
@@ -8514,6 +8544,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>912.4969484235231</v>
+      </c>
+      <c r="W27" t="n">
+        <v>239.7566088528665</v>
+      </c>
+      <c r="X27" t="n">
+        <v>916.6652623431328</v>
       </c>
     </row>
     <row r="28">
@@ -8532,10 +8568,10 @@
         <v>55.91135275705602</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>53.16934648261312</v>
+        <v>11.97438938058102</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>128.8598264409572</v>
+        <v>16.42153447798333</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>36.65335736122391</v>
@@ -8564,11 +8600,9 @@
       <c r="O28" s="2" t="n">
         <v>46.8245148185259</v>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" s="2" t="n">
         <v>-41.14463363308769</v>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" s="2" t="n">
         <v>56.77193739974499</v>
       </c>
@@ -8580,6 +8614,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>52.04538846348984</v>
+      </c>
+      <c r="W28" t="n">
+        <v>53.16934648261311</v>
+      </c>
+      <c r="X28" t="n">
+        <v>128.8598264409572</v>
       </c>
     </row>
     <row r="29">
@@ -8598,10 +8638,10 @@
         <v>133.9985194899797</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.0426205955792</v>
+        <v>20.5341410932543</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>239.4948007265725</v>
+        <v>24.95919633439684</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>9.564912687377998</v>
@@ -8630,11 +8670,9 @@
       <c r="O29" s="2" t="n">
         <v>13.58206358593469</v>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" s="2" t="n">
         <v>-21.97888064869188</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" s="2" t="n">
         <v>32.818431201824</v>
       </c>
@@ -8646,6 +8684,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>15.74045856603944</v>
+      </c>
+      <c r="W29" t="n">
+        <v>126.0426205955791</v>
+      </c>
+      <c r="X29" t="n">
+        <v>239.4948007265725</v>
       </c>
     </row>
     <row r="30">
@@ -8664,10 +8708,10 @@
         <v>702.7898111342278</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>647.5128651160256</v>
+        <v>57.09078875037612</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1317.654869615451</v>
+        <v>65.11338596173712</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>236.4219252063517</v>
@@ -8696,11 +8740,9 @@
       <c r="O30" s="2" t="n">
         <v>830.075714722672</v>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" s="2" t="n">
         <v>-274.3379403886319</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" s="2" t="n">
         <v>230.551840189872</v>
       </c>
@@ -8712,6 +8754,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>1052.784035982254</v>
+      </c>
+      <c r="W30" t="n">
+        <v>647.5128651160254</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1317.65486961545</v>
       </c>
     </row>
     <row r="31">
@@ -8730,10 +8778,10 @@
         <v>171.7908387157589</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>161.0901505358918</v>
+        <v>23.93611564556582</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>250.0620601628808</v>
+        <v>26.87279264958735</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>159.553158742494</v>
@@ -8762,11 +8810,9 @@
       <c r="O31" s="2" t="n">
         <v>225.0866553755816</v>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" s="2" t="n">
         <v>-99.10116842944521</v>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" s="2" t="n">
         <v>120.2403170835649</v>
       </c>
@@ -8778,6 +8824,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>264.6352371056698</v>
+      </c>
+      <c r="W31" t="n">
+        <v>161.0901505358917</v>
+      </c>
+      <c r="X31" t="n">
+        <v>250.0620601628806</v>
       </c>
     </row>
     <row r="32">
@@ -8796,10 +8848,10 @@
         <v>79.85991930173947</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>75.60582868852758</v>
+        <v>14.92061938419742</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>172.39955381522</v>
+        <v>20.11318207147856</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>32.65408222530078</v>
@@ -8828,11 +8880,9 @@
       <c r="O32" s="2" t="n">
         <v>43.6731753356332</v>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" s="2" t="n">
         <v>-46.60849345227933</v>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" s="2" t="n">
         <v>60.48894829312388</v>
       </c>
@@ -8844,6 +8894,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>49.22352449576737</v>
+      </c>
+      <c r="W32" t="n">
+        <v>75.60582868852757</v>
+      </c>
+      <c r="X32" t="n">
+        <v>172.3995538152199</v>
       </c>
     </row>
     <row r="33">
@@ -8862,10 +8918,10 @@
         <v>110.7342890438909</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>104.4081808479688</v>
+        <v>18.25474357106502</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>186.9682092644938</v>
+        <v>22.03883293856293</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>36.03175840738496</v>
@@ -8894,11 +8950,9 @@
       <c r="O33" s="2" t="n">
         <v>48.1539278679718</v>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" s="2" t="n">
         <v>-60.84991334101634</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" s="2" t="n">
         <v>76.49407141100848</v>
       </c>
@@ -8910,6 +8964,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>54.37521282713333</v>
+      </c>
+      <c r="W33" t="n">
+        <v>104.4081808479688</v>
+      </c>
+      <c r="X33" t="n">
+        <v>186.9682092644937</v>
       </c>
     </row>
     <row r="34">
@@ -8928,10 +8988,10 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.716344455020112</v>
+        <v>4.140247013315538</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7.967402453116491</v>
+        <v>3.39500255091874</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>8.646561330849892</v>
@@ -8960,11 +9020,9 @@
       <c r="O34" s="2" t="n">
         <v>-6.02916332238322e-13</v>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" s="2" t="n">
         <v>-52.69050758558471</v>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" s="2" t="n">
         <v>90.22878749527139</v>
       </c>
@@ -8976,6 +9034,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>9.71634445502011</v>
+      </c>
+      <c r="X34" t="n">
+        <v>7.967402453116489</v>
       </c>
     </row>
     <row r="35">
@@ -8994,10 +9058,10 @@
         <v>104.843321690143</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>98.92131414100946</v>
+        <v>17.64926811588385</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>235.0899712829863</v>
+        <v>23.45064399079919</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>286887.9181832359</v>
@@ -9026,11 +9090,9 @@
       <c r="O35" s="2" t="n">
         <v>381475.864896308</v>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" s="2" t="n">
         <v>-30.41509917676913</v>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" s="2" t="n">
         <v>36.10975889202988</v>
       </c>
@@ -9042,6 +9104,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>432377.2805293642</v>
+      </c>
+      <c r="W35" t="n">
+        <v>98.92131414100943</v>
+      </c>
+      <c r="X35" t="n">
+        <v>235.0899712829863</v>
       </c>
     </row>
     <row r="36">
@@ -9060,10 +9128,10 @@
         <v>83.73685906742837</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>79.22929469618578</v>
+        <v>15.36349646409256</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>157.1502738604991</v>
+        <v>19.073251182547</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>19.20734449602556</v>
@@ -9092,11 +9160,9 @@
       <c r="O36" s="2" t="n">
         <v>30.43362203042686</v>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" s="2" t="n">
         <v>-40.63373644380147</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" s="2" t="n">
         <v>47.97248906254866</v>
       </c>
@@ -9108,6 +9174,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>34.44567748145593</v>
+      </c>
+      <c r="W36" t="n">
+        <v>79.22929469618576</v>
+      </c>
+      <c r="X36" t="n">
+        <v>157.150273860499</v>
       </c>
     </row>
     <row r="37">
@@ -9126,10 +9198,10 @@
         <v>17.78279410038923</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17.15452227875549</v>
+        <v>5.905855485285083</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>26.75877418978885</v>
+        <v>6.640649609560725</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>4.139407490470938</v>
@@ -9158,11 +9230,9 @@
       <c r="O37" s="2" t="n">
         <v>5.92546502753431</v>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" s="2" t="n">
         <v>-10.46046395243107</v>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" s="2" t="n">
         <v>19.47314003852793</v>
       </c>
@@ -9174,6 +9244,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>6.798716360355339</v>
+      </c>
+      <c r="W37" t="n">
+        <v>17.15452227875548</v>
+      </c>
+      <c r="X37" t="n">
+        <v>26.75877418978884</v>
       </c>
     </row>
     <row r="38">
@@ -9192,10 +9268,10 @@
         <v>14.12537544622754</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.66558846732499</v>
+        <v>5.123658674783376</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>19.94180229588136</v>
+        <v>5.640488571062651</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>4.613541654033444</v>
@@ -9224,11 +9300,9 @@
       <c r="O38" s="2" t="n">
         <v>6.02185572619858</v>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" s="2" t="n">
         <v>-6.791482097398088</v>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" s="2" t="n">
         <v>12.97560648514676</v>
       </c>
@@ -9240,6 +9314,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>6.701891479903765</v>
+      </c>
+      <c r="W38" t="n">
+        <v>13.66558846732499</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.94180229588135</v>
       </c>
     </row>
     <row r="39">
@@ -9258,10 +9338,10 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>9.716344455020112</v>
+        <v>4.140247013315538</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>8.015984175391592</v>
+        <v>3.415703785985318</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>3.449196327996785</v>
@@ -9290,11 +9370,9 @@
       <c r="O39" s="2" t="n">
         <v>6.23187373681345</v>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" s="2" t="n">
         <v>-20.15516180778258</v>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" s="2" t="n">
         <v>36.91993923330198</v>
       </c>
@@ -9306,6 +9384,12 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>7.435466290384134</v>
+      </c>
+      <c r="W39" t="n">
+        <v>9.71634445502011</v>
+      </c>
+      <c r="X39" t="n">
+        <v>8.015984175391591</v>
       </c>
     </row>
     <row r="40">
@@ -9356,11 +9440,9 @@
       <c r="O40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" s="2" t="n">
         <v>1</v>
       </c>
@@ -9371,6 +9453,12 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9422,11 +9510,9 @@
       <c r="O41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" s="2" t="n">
         <v>1</v>
       </c>
@@ -9437,6 +9523,12 @@
         <v>1</v>
       </c>
       <c r="V41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9451,7 +9543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9589,6 +9681,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -9638,19 +9740,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9702,11 +9807,9 @@
       <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" s="2" t="n">
         <v>-4.497969730785198</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" s="2" t="n">
         <v>11.00350975195064</v>
       </c>
@@ -9718,6 +9821,12 @@
       </c>
       <c r="V3" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -9768,11 +9877,9 @@
       <c r="O4" s="2" t="n">
         <v>0.3042852088602729</v>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" s="2" t="n">
         <v>-1.126229271969796</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" s="2" t="n">
         <v>11.00350975195064</v>
       </c>
@@ -9784,6 +9891,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0.3042852088602723</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -9834,11 +9947,9 @@
       <c r="O5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" s="2" t="n">
         <v>11.00350975195064</v>
       </c>
@@ -9850,6 +9961,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -9900,11 +10017,9 @@
       <c r="O6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" s="2" t="n">
         <v>-3.070894912027654</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" s="2" t="n">
         <v>11.00350975195065</v>
       </c>
@@ -9916,6 +10031,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -9934,10 +10055,10 @@
         <v>991.1394114273684</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>909.2676876500602</v>
+        <v>70.58197301449189</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2094.892902187049</v>
+        <v>92.56058686811353</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -9966,11 +10087,9 @@
       <c r="O7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" s="2" t="n">
         <v>-601.0112173140612</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" s="2" t="n">
         <v>569.8501826354508</v>
       </c>
@@ -9982,6 +10101,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>909.2676876500599</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2094.892902187048</v>
       </c>
     </row>
     <row r="8">
@@ -10000,10 +10125,10 @@
         <v>275.5520862134852</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>256.8669565779018</v>
+        <v>32.03832086819186</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1020.924660915442</v>
+        <v>50.79257546096126</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
@@ -10032,11 +10157,9 @@
       <c r="O8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" s="2" t="n">
         <v>-741.7586496912562</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" s="2" t="n">
         <v>953.7756558591195</v>
       </c>
@@ -10048,6 +10171,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>256.8669565779015</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1020.924660915441</v>
       </c>
     </row>
     <row r="9">
@@ -10066,10 +10195,10 @@
         <v>1347.512651739257</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1231.466989345203</v>
+        <v>85.31078291082535</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6584.935054668646</v>
+        <v>160.6911547254937</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -10098,11 +10227,9 @@
       <c r="O9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" s="2" t="n">
         <v>-35005.9841941941</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" s="2" t="n">
         <v>27271.28667430043</v>
       </c>
@@ -10114,6 +10241,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1231.466989345202</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6584.935054668641</v>
       </c>
     </row>
     <row r="10">
@@ -10132,10 +10265,10 @@
         <v>530.1130576685345</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>490.1418699926787</v>
+        <v>47.97410565466274</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1481.064720503728</v>
+        <v>71.51627913010259</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -10164,11 +10297,9 @@
       <c r="O10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" s="2" t="n">
         <v>-15927.1786414388</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" s="2" t="n">
         <v>16564.87014846044</v>
       </c>
@@ -10180,6 +10311,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>490.1418699926785</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1481.064720503728</v>
       </c>
     </row>
     <row r="11">
@@ -10198,10 +10335,10 @@
         <v>791.4867217282414</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>728.1510850960457</v>
+        <v>61.43499302912673</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1674.546999207294</v>
+        <v>82.78084510090028</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -10230,11 +10367,9 @@
       <c r="O11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" s="2" t="n">
         <v>-74223.08530919842</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" s="2" t="n">
         <v>76977.82354942671</v>
       </c>
@@ -10246,6 +10381,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>728.1510850960461</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1674.546999207293</v>
       </c>
     </row>
     <row r="12">
@@ -10264,10 +10405,10 @@
         <v>2800.516288983121</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2536.04895514903</v>
+        <v>133.9789001764712</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>9821.426827373803</v>
+        <v>212.9472980556079</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>3417.612265190938</v>
@@ -10296,11 +10437,9 @@
       <c r="O12" s="2" t="n">
         <v>7596.014295076567</v>
       </c>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" s="2" t="n">
         <v>-1524.487507841139</v>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" s="2" t="n">
         <v>1166.999332539039</v>
       </c>
@@ -10312,6 +10451,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>9391.662138688902</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2536.048955149029</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9821.426827373798</v>
       </c>
     </row>
     <row r="13">
@@ -10330,10 +10475,10 @@
         <v>117.3184317678517</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>110.5363646963467</v>
+        <v>18.91704521019124</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>251.1727815471478</v>
+        <v>22.63912754818824</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>91.87678219715164</v>
@@ -10362,11 +10507,9 @@
       <c r="O13" s="2" t="n">
         <v>74.4819607216869</v>
       </c>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" s="2" t="n">
         <v>-374.3886569028667</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" s="2" t="n">
         <v>499.7184574478964</v>
       </c>
@@ -10378,6 +10521,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>84.26381301195687</v>
+      </c>
+      <c r="W13" t="n">
+        <v>110.5363646963466</v>
+      </c>
+      <c r="X13" t="n">
+        <v>251.1727815471477</v>
       </c>
     </row>
     <row r="14">
@@ -10396,10 +10545,10 @@
         <v>190.4081560092463</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>178.3183738036412</v>
+        <v>25.50502949857076</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>351.9155656720407</v>
+        <v>30.90062678915925</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>90.72503142743354</v>
@@ -10428,11 +10577,9 @@
       <c r="O14" s="2" t="n">
         <v>110.6370695097425</v>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" s="2" t="n">
         <v>-88.56025196521966</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" s="2" t="n">
         <v>122.5788765579871</v>
       </c>
@@ -10444,6 +10591,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>126.7677064564085</v>
+      </c>
+      <c r="W14" t="n">
+        <v>178.3183738036411</v>
+      </c>
+      <c r="X14" t="n">
+        <v>351.9155656720405</v>
       </c>
     </row>
     <row r="15">
@@ -10462,10 +10615,10 @@
         <v>206.3558002114387</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>193.0592836509582</v>
+        <v>26.80274388342972</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>691.7394369840722</v>
+        <v>39.9303215569841</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3058.910029655324</v>
@@ -10494,11 +10647,9 @@
       <c r="O15" s="2" t="n">
         <v>4951.016718602047</v>
       </c>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" s="2" t="n">
         <v>-356.7876843021971</v>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" s="2" t="n">
         <v>454.5545198186172</v>
       </c>
@@ -10510,6 +10661,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>5872.867165714218</v>
+      </c>
+      <c r="W15" t="n">
+        <v>193.0592836509578</v>
+      </c>
+      <c r="X15" t="n">
+        <v>691.7394369840717</v>
       </c>
     </row>
     <row r="16">
@@ -10528,10 +10685,10 @@
         <v>150.4468635259402</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>141.3097633252641</v>
+        <v>22.05477127058738</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>345.6084813270808</v>
+        <v>27.68204665267317</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>95.13459497397281</v>
@@ -10560,11 +10717,9 @@
       <c r="O16" s="2" t="n">
         <v>85.35849224454691</v>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" s="2" t="n">
         <v>-290.0195995918539</v>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" s="2" t="n">
         <v>400.5862138331403</v>
       </c>
@@ -10576,6 +10731,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>95.42795852018388</v>
+      </c>
+      <c r="W16" t="n">
+        <v>141.309763325264</v>
+      </c>
+      <c r="X16" t="n">
+        <v>345.6084813270807</v>
       </c>
     </row>
     <row r="17">
@@ -10594,10 +10755,10 @@
         <v>1310.103589747261</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1197.700868625728</v>
+        <v>83.84157247118402</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5858.158548750411</v>
+        <v>150.1475738309802</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>337261.0640296775</v>
@@ -10626,11 +10787,9 @@
       <c r="O17" s="2" t="n">
         <v>447352.6497241581</v>
       </c>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" s="2" t="n">
         <v>-1360.122885056331</v>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" s="2" t="n">
         <v>1398.027199192025</v>
       </c>
@@ -10642,6 +10801,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>528322.7833985733</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1197.700868625727</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5858.158548750407</v>
       </c>
     </row>
     <row r="18">
@@ -10660,10 +10825,10 @@
         <v>40.75628967116911</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>38.9109542065526</v>
+        <v>9.852180611192738</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>257.9894018611116</v>
+        <v>18.23404557889487</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>240519.7708361118</v>
@@ -10692,11 +10857,9 @@
       <c r="O18" s="2" t="n">
         <v>319786.5044755135</v>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" s="2" t="n">
         <v>-98.45384278795338</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" s="2" t="n">
         <v>140.9809849150921</v>
       </c>
@@ -10708,6 +10871,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>368059.0505787696</v>
+      </c>
+      <c r="W18" t="n">
+        <v>38.91095420655259</v>
+      </c>
+      <c r="X18" t="n">
+        <v>257.9894018611114</v>
       </c>
     </row>
     <row r="19">
@@ -10726,10 +10895,10 @@
         <v>227.6721074390069</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>212.7405595194875</v>
+        <v>28.47882382785136</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1454.477273885661</v>
+        <v>52.84739370330574</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5850.040025610309</v>
@@ -10758,11 +10927,9 @@
       <c r="O19" s="2" t="n">
         <v>7955.355086625216</v>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" s="2" t="n">
         <v>-475.3042283301512</v>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" s="2" t="n">
         <v>558.607592273578</v>
       </c>
@@ -10774,6 +10941,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>9372.190554609972</v>
+      </c>
+      <c r="W19" t="n">
+        <v>212.7405595194874</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1454.47727388566</v>
       </c>
     </row>
     <row r="20">
@@ -10792,10 +10965,10 @@
         <v>28.84031503126606</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>27.65376308392867</v>
+        <v>7.958996774982072</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>83.33437473728972</v>
+        <v>11.82535459198235</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>22.31942905594573</v>
@@ -10824,11 +10997,9 @@
       <c r="O20" s="2" t="n">
         <v>27.46092768324986</v>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" s="2" t="n">
         <v>-14.11061804876872</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" s="2" t="n">
         <v>30.88129191428204</v>
       </c>
@@ -10840,6 +11011,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>30.24186607511134</v>
+      </c>
+      <c r="W20" t="n">
+        <v>27.65376308392866</v>
+      </c>
+      <c r="X20" t="n">
+        <v>83.33437473728969</v>
       </c>
     </row>
     <row r="21">
@@ -10858,10 +11035,10 @@
         <v>734.4818583377563</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>676.3393077380938</v>
+        <v>58.66587620713965</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2059.00128028696</v>
+        <v>85.17639378034298</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>348.1002678143789</v>
@@ -10890,11 +11067,9 @@
       <c r="O21" s="2" t="n">
         <v>354.7548125968916</v>
       </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" s="2" t="n">
         <v>-898.8530693244892</v>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" s="2" t="n">
         <v>998.7707895052965</v>
       </c>
@@ -10906,6 +11081,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>404.581424731353</v>
+      </c>
+      <c r="W21" t="n">
+        <v>676.3393077380936</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2059.001280286959</v>
       </c>
     </row>
     <row r="22">
@@ -10924,10 +11105,10 @@
         <v>2043.792593773252</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1858.08667865269</v>
+        <v>110.3129315338512</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>9333.678450531403</v>
+        <v>196.2348560208155</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>33722.92680576551</v>
@@ -10956,11 +11137,9 @@
       <c r="O22" s="2" t="n">
         <v>47006.29229574183</v>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" s="2" t="n">
         <v>-1659.711482891244</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" s="2" t="n">
         <v>1361.516609944671</v>
       </c>
@@ -10972,6 +11151,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>54529.85719269228</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1858.086678652689</v>
+      </c>
+      <c r="X22" t="n">
+        <v>9333.678450531397</v>
       </c>
     </row>
     <row r="23">
@@ -10990,10 +11175,10 @@
         <v>684.9096007862478</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>631.242264454877</v>
+        <v>56.19014597439239</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1744.520378125776</v>
+        <v>80.90748247350828</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>2377.721504583104</v>
@@ -11022,11 +11207,9 @@
       <c r="O23" s="2" t="n">
         <v>3236.292638276838</v>
       </c>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" s="2" t="n">
         <v>-340.257531540153</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" s="2" t="n">
         <v>374.8451208848804</v>
       </c>
@@ -11038,6 +11221,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>3797.612340999315</v>
+      </c>
+      <c r="W23" t="n">
+        <v>631.2422644548756</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1744.520378125776</v>
       </c>
     </row>
     <row r="24">
@@ -11056,10 +11245,10 @@
         <v>457.1259612054471</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>423.4412461107</v>
+        <v>43.78365113542493</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1666.94769528474</v>
+        <v>71.04205569888663</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>393.8336454302723</v>
@@ -11088,11 +11277,9 @@
       <c r="O24" s="2" t="n">
         <v>731.7701456153364</v>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" s="2" t="n">
         <v>-340.6025323183841</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" s="2" t="n">
         <v>292.9608004273715</v>
       </c>
@@ -11104,6 +11291,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>879.9238041237845</v>
+      </c>
+      <c r="W24" t="n">
+        <v>423.4412461106999</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1666.947695284739</v>
       </c>
     </row>
     <row r="25">
@@ -11122,10 +11315,10 @@
         <v>721.5611730784314</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>664.5888305031265</v>
+        <v>58.02692732730644</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1923.880476698552</v>
+        <v>84.08158774327518</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>707.7862607968668</v>
@@ -11154,11 +11347,9 @@
       <c r="O25" s="2" t="n">
         <v>1280.174580874365</v>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" s="2" t="n">
         <v>-479.7941644850852</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" s="2" t="n">
         <v>483.3775449695071</v>
       </c>
@@ -11170,6 +11361,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>1536.980813788296</v>
+      </c>
+      <c r="W25" t="n">
+        <v>664.5888305031262</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1923.88047669855</v>
       </c>
     </row>
     <row r="26">
@@ -11188,10 +11385,10 @@
         <v>367.1023673046354</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>340.9846193549697</v>
+        <v>38.24203771105975</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1026.554481073546</v>
+        <v>57.14051915294576</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1462.563583856809</v>
@@ -11220,11 +11417,9 @@
       <c r="O26" s="2" t="n">
         <v>1951.049027765728</v>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" s="2" t="n">
         <v>-337.3551950946617</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" s="2" t="n">
         <v>354.1142892986752</v>
       </c>
@@ -11236,6 +11431,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>2206.173007621883</v>
+      </c>
+      <c r="W26" t="n">
+        <v>340.9846193549695</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1026.554481073546</v>
       </c>
     </row>
     <row r="27">
@@ -11254,10 +11455,10 @@
         <v>256.9728150281728</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>239.7566088528666</v>
+        <v>30.68765174730518</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>917.1833187884677</v>
+        <v>51.63295810289328</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>603.9567976377734</v>
@@ -11286,11 +11487,9 @@
       <c r="O27" s="2" t="n">
         <v>799.9153437413603</v>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" s="2" t="n">
         <v>-225.0329317747712</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" s="2" t="n">
         <v>207.8973048360189</v>
       </c>
@@ -11302,6 +11501,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>914.4877172888382</v>
+      </c>
+      <c r="W27" t="n">
+        <v>239.7566088528665</v>
+      </c>
+      <c r="X27" t="n">
+        <v>917.1833187884672</v>
       </c>
     </row>
     <row r="28">
@@ -11320,10 +11525,10 @@
         <v>55.91135275705602</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>53.16934648261312</v>
+        <v>11.97438938058102</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>129.3456436637082</v>
+        <v>16.62854682864911</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>37.20891293149666</v>
@@ -11352,11 +11557,9 @@
       <c r="O28" s="2" t="n">
         <v>47.38007038879867</v>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" s="2" t="n">
         <v>-40.64463363308769</v>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" s="2" t="n">
         <v>57.09693739974499</v>
       </c>
@@ -11368,6 +11571,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>52.60220453997403</v>
+      </c>
+      <c r="W28" t="n">
+        <v>53.16934648261311</v>
+      </c>
+      <c r="X28" t="n">
+        <v>129.3456436637082</v>
       </c>
     </row>
     <row r="29">
@@ -11386,10 +11595,10 @@
         <v>133.9985194899797</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.0426205955792</v>
+        <v>20.5341410932543</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>240.4664351720746</v>
+        <v>25.37322103572839</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>9.809710721206983</v>
@@ -11418,11 +11627,9 @@
       <c r="O29" s="2" t="n">
         <v>13.82686161976365</v>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" s="2" t="n">
         <v>-21.74632251947257</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" s="2" t="n">
         <v>33.00447770519945</v>
       </c>
@@ -11434,6 +11641,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>15.98764928155265</v>
+      </c>
+      <c r="W29" t="n">
+        <v>126.0426205955791</v>
+      </c>
+      <c r="X29" t="n">
+        <v>240.4664351720745</v>
       </c>
     </row>
     <row r="30">
@@ -11452,10 +11665,10 @@
         <v>702.7898111342278</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>647.5128651160256</v>
+        <v>57.09078875037612</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1318.510929057123</v>
+        <v>65.26882160735876</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>236.5651159850398</v>
@@ -11484,11 +11697,9 @@
       <c r="O30" s="2" t="n">
         <v>831.7450409531613</v>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" s="2" t="n">
         <v>-273.7665483713752</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" s="2" t="n">
         <v>230.7619429320222</v>
       </c>
@@ -11500,6 +11711,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>1054.680271904452</v>
+      </c>
+      <c r="W30" t="n">
+        <v>647.5128651160254</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1318.510929057122</v>
       </c>
     </row>
     <row r="31">
@@ -11518,10 +11735,10 @@
         <v>171.7908387157589</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>161.0901505358918</v>
+        <v>23.93611564556582</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>250.0620601628808</v>
+        <v>26.87279264958735</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>159.553158742494</v>
@@ -11550,11 +11767,9 @@
       <c r="O31" s="2" t="n">
         <v>225.0866553755816</v>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" s="2" t="n">
         <v>-99.10116842944521</v>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" s="2" t="n">
         <v>120.2403170835649</v>
       </c>
@@ -11566,6 +11781,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>264.6352371056698</v>
+      </c>
+      <c r="W31" t="n">
+        <v>161.0901505358917</v>
+      </c>
+      <c r="X31" t="n">
+        <v>250.0620601628806</v>
       </c>
     </row>
     <row r="32">
@@ -11584,10 +11805,10 @@
         <v>79.85991930173947</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>75.60582868852758</v>
+        <v>14.92061938419742</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>172.39955381522</v>
+        <v>20.11318207147856</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>32.65408222530078</v>
@@ -11616,11 +11837,9 @@
       <c r="O32" s="2" t="n">
         <v>43.67317533563319</v>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" s="2" t="n">
         <v>-46.60849345227933</v>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" s="2" t="n">
         <v>60.48894829312388</v>
       </c>
@@ -11632,6 +11851,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>49.22352449576737</v>
+      </c>
+      <c r="W32" t="n">
+        <v>75.60582868852757</v>
+      </c>
+      <c r="X32" t="n">
+        <v>172.3995538152199</v>
       </c>
     </row>
     <row r="33">
@@ -11650,10 +11875,10 @@
         <v>110.7342890438909</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>104.4081808479688</v>
+        <v>18.25474357106502</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>186.9682092644938</v>
+        <v>22.03883293856293</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>36.03175840738496</v>
@@ -11682,11 +11907,9 @@
       <c r="O33" s="2" t="n">
         <v>48.15392786797182</v>
       </c>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" s="2" t="n">
         <v>-60.84991334101634</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" s="2" t="n">
         <v>76.49407141100848</v>
       </c>
@@ -11698,6 +11921,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>54.37521282713333</v>
+      </c>
+      <c r="W33" t="n">
+        <v>104.4081808479688</v>
+      </c>
+      <c r="X33" t="n">
+        <v>186.9682092644937</v>
       </c>
     </row>
     <row r="34">
@@ -11716,10 +11945,10 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>9.716344455020112</v>
+        <v>4.140247013315538</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>9.230527232269106</v>
+        <v>3.93323466264976</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>10.01735763939926</v>
@@ -11748,11 +11977,9 @@
       <c r="O34" s="2" t="n">
         <v>2.899495361929437</v>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" s="2" t="n">
         <v>-50.83336455133091</v>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" s="2" t="n">
         <v>91.52878760375184</v>
       </c>
@@ -11764,6 +11991,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>3.093012786806117</v>
+      </c>
+      <c r="W34" t="n">
+        <v>9.71634445502011</v>
+      </c>
+      <c r="X34" t="n">
+        <v>9.230527232269104</v>
       </c>
     </row>
     <row r="35">
@@ -11782,10 +12015,10 @@
         <v>104.843321690143</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>98.92131414100946</v>
+        <v>17.64926811588385</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>235.0899712829863</v>
+        <v>23.45064399079919</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>286887.9181832359</v>
@@ -11814,11 +12047,9 @@
       <c r="O35" s="2" t="n">
         <v>381475.864896308</v>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" s="2" t="n">
         <v>-30.41509917676913</v>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" s="2" t="n">
         <v>36.10975889202988</v>
       </c>
@@ -11830,6 +12061,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>432377.2805293642</v>
+      </c>
+      <c r="W35" t="n">
+        <v>98.92131414100943</v>
+      </c>
+      <c r="X35" t="n">
+        <v>235.0899712829863</v>
       </c>
     </row>
     <row r="36">
@@ -11848,10 +12085,10 @@
         <v>83.73685906742837</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>79.22929469618578</v>
+        <v>15.36349646409256</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>157.1502738604991</v>
+        <v>19.073251182547</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>19.20734449602556</v>
@@ -11880,11 +12117,9 @@
       <c r="O36" s="2" t="n">
         <v>30.43362203042686</v>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" s="2" t="n">
         <v>-40.63373644380147</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" s="2" t="n">
         <v>47.97248906254866</v>
       </c>
@@ -11896,6 +12131,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>34.44567748145593</v>
+      </c>
+      <c r="W36" t="n">
+        <v>79.22929469618576</v>
+      </c>
+      <c r="X36" t="n">
+        <v>157.150273860499</v>
       </c>
     </row>
     <row r="37">
@@ -11914,10 +12155,10 @@
         <v>17.78279410038923</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17.15452227875549</v>
+        <v>5.905855485285083</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>26.75877418978885</v>
+        <v>6.640649609560725</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>4.139407490470938</v>
@@ -11946,11 +12187,9 @@
       <c r="O37" s="2" t="n">
         <v>5.92546502753431</v>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" s="2" t="n">
         <v>-10.46046395243107</v>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" s="2" t="n">
         <v>19.47314003852793</v>
       </c>
@@ -11962,6 +12201,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>6.798716360355339</v>
+      </c>
+      <c r="W37" t="n">
+        <v>17.15452227875548</v>
+      </c>
+      <c r="X37" t="n">
+        <v>26.75877418978884</v>
       </c>
     </row>
     <row r="38">
@@ -11980,10 +12225,10 @@
         <v>14.12537544622754</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.66558846732499</v>
+        <v>5.123658674783376</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>19.94180229588136</v>
+        <v>5.640488571062651</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>4.613541654033444</v>
@@ -12012,11 +12257,9 @@
       <c r="O38" s="2" t="n">
         <v>6.021855726198582</v>
       </c>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" s="2" t="n">
         <v>-6.791482097398088</v>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" s="2" t="n">
         <v>12.97560648514676</v>
       </c>
@@ -12028,6 +12271,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>6.701891479903765</v>
+      </c>
+      <c r="W38" t="n">
+        <v>13.66558846732499</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.94180229588135</v>
       </c>
     </row>
     <row r="39">
@@ -12046,10 +12295,10 @@
         <v>10</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>9.716344455020112</v>
+        <v>4.140247013315538</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>8.015984175391592</v>
+        <v>3.415703785985318</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>3.449196327996785</v>
@@ -12078,11 +12327,9 @@
       <c r="O39" s="2" t="n">
         <v>6.231873736813448</v>
       </c>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" s="2" t="n">
         <v>-20.15516180778258</v>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" s="2" t="n">
         <v>36.91993923330198</v>
       </c>
@@ -12094,6 +12341,12 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>7.435466290384134</v>
+      </c>
+      <c r="W39" t="n">
+        <v>9.71634445502011</v>
+      </c>
+      <c r="X39" t="n">
+        <v>8.015984175391591</v>
       </c>
     </row>
     <row r="40">
@@ -12144,11 +12397,9 @@
       <c r="O40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" s="2" t="n">
         <v>1</v>
       </c>
@@ -12159,6 +12410,12 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12210,11 +12467,9 @@
       <c r="O41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" s="2" t="n">
         <v>1</v>
       </c>
@@ -12225,6 +12480,12 @@
         <v>1</v>
       </c>
       <c r="V41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12715,7 +12976,6 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>1.59176568425259</v>
       </c>
@@ -12850,7 +13110,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Northern_Humboldt_Current (1995-1998)</t>
@@ -12914,7 +13173,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -13117,7 +13375,6 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>1.109823001872164</v>
       </c>
@@ -13228,7 +13485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13289,14 +13546,12 @@
       <c r="C2" s="2" t="n">
         <v>3566.092845824302</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>11273.05644750595</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.316337708626773</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -13310,14 +13565,12 @@
       <c r="C3" s="2" t="n">
         <v>4420.246977695257</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>11273.05644750595</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.3921072335864327</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -13326,19 +13579,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4145.947665640842</v>
+        <v>654.1516107106142</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4145.947665640842</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>654.1516107106142</v>
+      </c>
       <c r="E4" s="2" t="n">
         <v>11273.05644750595</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.3677749406247399</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.05802788389792359</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -13347,22 +13598,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11307.03105039657</v>
+        <v>906.9046759566413</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11292.79854155715</v>
+        <v>904.4437922575739</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7431.800095064604</v>
+        <v>693.6790158219734</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>11273.05644750595</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1.001751263656235</v>
+        <v>0.08023057424303708</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6592533382292088</v>
+        <v>0.06153424486537037</v>
       </c>
     </row>
     <row r="6">
@@ -13596,12 +13847,6 @@
           <t>sym_TE_asDC</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -13634,12 +13879,6 @@
           <t>sym_GE_asDC</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -13739,6 +13978,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.8894829681654792</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4145.947665640841</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4145.947665640841</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11273.05644750595</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3677749406247398</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11307.03105039656</v>
+      </c>
+      <c r="C23" t="n">
+        <v>11292.79854155715</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7431.800095064602</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11273.05644750595</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.001751263656234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.6592533382292086</v>
       </c>
     </row>
   </sheetData>
@@ -13874,7 +14157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13910,7 +14193,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -13923,7 +14205,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -13936,7 +14217,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -13949,7 +14229,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -13962,7 +14241,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -13975,7 +14253,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -13988,7 +14265,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -14001,7 +14277,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -14014,7 +14289,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -14058,7 +14332,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14075,7 +14349,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14351,6 +14625,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
